--- a/docs/xlsx/jobs-2026-09-22.xlsx
+++ b/docs/xlsx/jobs-2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="565">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1684 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Advancement Director</t>
+  </si>
+  <si>
+    <t>Coastal Rivers Conservation Trust</t>
+  </si>
+  <si>
+    <t>Damariscotta, ME</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$100,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-advancement-director-damariscotta-maine/5897088092</t>
+  </si>
+  <si>
+    <t>Archaeological Field Director</t>
+  </si>
+  <si>
+    <t>North Wind Resource Consulting</t>
+  </si>
+  <si>
+    <t>Tempe, AZ</t>
+  </si>
+  <si>
+    <t>$70,000 - $83,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archaeological-field-director-tempe-arizona/2221431120</t>
+  </si>
+  <si>
+    <t>Archaeology Field Director/Laboratory Director</t>
+  </si>
+  <si>
+    <t>$72,000 - $83,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archaeology-field-directorlaboratory-director-tempe-arizona/2959489532</t>
+  </si>
+  <si>
+    <t>Boundary Marking Crew Member</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$480 per week</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-boundary-marking-crew-member-chattanooga-tennessee/3052020116</t>
+  </si>
+  <si>
+    <t>Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,250 in the first year.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campaign-organizer-denver-colorado/3284071105</t>
+  </si>
+  <si>
+    <t>Canvass Office Director</t>
+  </si>
+  <si>
+    <t>Fund for the Public Interest</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this position is $40,000-$53,750, depending on position and location.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-boston-massachusetts/1198234121</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-seattle-washington/7500014067</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-oakland-california/5620820377</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-philadelphia-pennsylvania/9219856864</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-portland-oregon/3178853966</t>
+  </si>
+  <si>
+    <t>Santa Cruz, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-santa-cruz-california/8241406165</t>
+  </si>
+  <si>
+    <t>Conservation Director</t>
+  </si>
+  <si>
+    <t>Nevada Land Trust</t>
+  </si>
+  <si>
+    <t>Reno, NV</t>
+  </si>
+  <si>
+    <t>$90,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-director-reno-nevada/3638939092</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Saltwater Inc</t>
+  </si>
+  <si>
+    <t>Woods Hole, MA</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-analyst-woods-hole-massachusetts/7940822840</t>
+  </si>
+  <si>
+    <t>Design Manager</t>
+  </si>
+  <si>
+    <t>Ipswich River Watershed Association</t>
+  </si>
+  <si>
+    <t>Ipswich, MA</t>
+  </si>
+  <si>
+    <t>$60,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-design-manager-ipswich-massachusetts/6967334853</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>EcoForesters</t>
+  </si>
+  <si>
+    <t>Asheville, NC</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-director-asheville-north-carolina/8216867672</t>
+  </si>
+  <si>
+    <t>District Forester (Lassen Forestry District)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Anderson, CA</t>
+  </si>
+  <si>
+    <t>$70,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-forester-lassen-forestry-district-anderson-california/8500404001</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Bainbridge Island Land Trust</t>
+  </si>
+  <si>
+    <t>Bainbridge Island, WA</t>
+  </si>
+  <si>
+    <t>$150,000 - $180,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-bainbridge-island-washington/7224204902</t>
+  </si>
+  <si>
+    <t>Fisheries Technician I-Hatchery, Tutka Bay Lagoon Hatchery</t>
+  </si>
+  <si>
+    <t>Cook Inlet Aquaculture Association</t>
+  </si>
+  <si>
+    <t>Homer, AK</t>
+  </si>
+  <si>
+    <t>$14.35 - $16.55 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-i-hatchery-tutka-bay-lagoon-hatchery-homer-alaska/9008141523</t>
+  </si>
+  <si>
+    <t>Fishery Biologist 1- American River Escapement Survey Crew Leader</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Rancho Cordova, CA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$21.71 - $34.96 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-1--american-river-escapement-survey-crew-leader-rancho-cordova-california/1668487239</t>
+  </si>
+  <si>
+    <t>Forest Conservation Coordinator | North Tri-State Position</t>
+  </si>
+  <si>
+    <t>Ruffed Grouse Society &amp; American Woodcock Society</t>
+  </si>
+  <si>
+    <t>Johnson City, TN</t>
+  </si>
+  <si>
+    <t>$60,000 - $84,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-conservation-coordinator--north-tri-state-position-johnson-city-tennessee/9962622558</t>
+  </si>
+  <si>
+    <t>Forestry Director</t>
+  </si>
+  <si>
+    <t>Placer Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Auburn, CA</t>
+  </si>
+  <si>
+    <t>$97,356 - $151,032 per year</t>
+  </si>
+  <si>
+    <t>forestry-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-director-auburn-california/1679668282</t>
+  </si>
+  <si>
+    <t>Habitat Specialist I (Conservation Technician)</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Elko &amp; Winnemucca, NV</t>
+  </si>
+  <si>
+    <t>$40,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-specialist-i-conservation-technician-elko--winnemucca-nevada/3333769649</t>
+  </si>
+  <si>
+    <t>Home Water &amp; Energy Efficiency Coordinator</t>
+  </si>
+  <si>
+    <t>Bridging The Gap, Inc.</t>
+  </si>
+  <si>
+    <t>Kansas City, MO</t>
+  </si>
+  <si>
+    <t>$44,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-home-water--energy-efficiency-coordinator-kansas-city-missouri/8704119407</t>
+  </si>
+  <si>
+    <t>Intergovernmental Affairs Analyst</t>
+  </si>
+  <si>
+    <t>Chilkat Indian Village (Klukwan)</t>
+  </si>
+  <si>
+    <t>Klukwan, Alaska, Remote</t>
+  </si>
+  <si>
+    <t>$66,650 - $79,040 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-intergovernmental-affairs-analyst-klukwan-alaska-remote/5975673168</t>
+  </si>
+  <si>
+    <t>INTERNSHIP- Environmental Education</t>
+  </si>
+  <si>
+    <t>Conservancy of Southwest Florida</t>
+  </si>
+  <si>
+    <t>Naples, FL</t>
+  </si>
+  <si>
+    <t>$150 per week</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-internship--environmental-education-naples-florida/2794134247</t>
+  </si>
+  <si>
+    <t>Laboratory Analyst</t>
+  </si>
+  <si>
+    <t>Eagle River Water &amp; Sanitation District</t>
+  </si>
+  <si>
+    <t>Vail, CO</t>
+  </si>
+  <si>
+    <t>$32.11 - $52.05 per hour</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-laboratory-analyst-vail-colorado/8468830251</t>
+  </si>
+  <si>
+    <t>Marine Science Instructor -- Shared Housing, Meals, and Ocean Fun included</t>
+  </si>
+  <si>
+    <t>Seacamp</t>
+  </si>
+  <si>
+    <t>Big Pine Key, FL</t>
+  </si>
+  <si>
+    <t>$1,100 - $1,300 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-science-instructor----shared-housing-meals-and-ocean-fun-included-big-pine-key-florida/9445927057</t>
+  </si>
+  <si>
+    <t>NOLS Teton Valley-Winter Program Supervisor</t>
+  </si>
+  <si>
+    <t>National Outdoor Leadership School (NOLS)</t>
+  </si>
+  <si>
+    <t>Driggs, ID</t>
+  </si>
+  <si>
+    <t>$41,404 - $44,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nols-teton-valley-winter-program-supervisor-driggs-idaho/7247894250</t>
+  </si>
+  <si>
+    <t>Plan Review Supervisor</t>
+  </si>
+  <si>
+    <t>City of Raleigh - Stormwater Management</t>
+  </si>
+  <si>
+    <t>Raleigh, NC</t>
+  </si>
+  <si>
+    <t>$90,640 - $115,507 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-plan-review-supervisor-raleigh-north-carolina/8247125659</t>
+  </si>
+  <si>
+    <t>Prescribed Fire Technician</t>
+  </si>
+  <si>
+    <t>The Orianne Society</t>
+  </si>
+  <si>
+    <t>Lumber City, GA</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-prescribed-fire-technician-lumber-city-georgia/9765509056</t>
+  </si>
+  <si>
+    <t>Private Lands Conservationist II</t>
+  </si>
+  <si>
+    <t>Clarkston, WA</t>
+  </si>
+  <si>
+    <t>$50,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-private-lands-conservationist-ii-clarkston-washington/7856963301</t>
+  </si>
+  <si>
+    <t>Range &amp; Wildlife Biologist I, II, or III</t>
+  </si>
+  <si>
+    <t>$40,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-range--wildlife-biologist-i-ii-or-iii-elko--winnemucca-nevada/8899798538</t>
+  </si>
+  <si>
+    <t>Research Data Specialist II</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$7,640 - $9,847 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-data-specialist-ii-sacramento-california/1150195252</t>
+  </si>
+  <si>
+    <t>Senior Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>Riverside, CA</t>
+  </si>
+  <si>
+    <t>$11,437 - $14,315 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-water-resource-control-engineer-riverside-california/7642420565</t>
+  </si>
+  <si>
+    <t>Staff Archaeologist</t>
+  </si>
+  <si>
+    <t>SWCA Environmental Consultants</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>$23.95 - $30.64 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-staff-archaeologist-albuquerque-new-mexico/8028111870</t>
+  </si>
+  <si>
+    <t>State Conservation Advocate</t>
+  </si>
+  <si>
+    <t>The target annual compensation for someone with 2-5 years of relevant experience is $41,750-$46,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-conservation-advocate-boston-massachusetts/2277044269</t>
+  </si>
+  <si>
+    <t>Stormwater Plan Review Engineer</t>
+  </si>
+  <si>
+    <t>$74,197 - $94,598 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stormwater-plan-review-engineer-raleigh-north-carolina/2738100901</t>
+  </si>
+  <si>
+    <t>Stream Restoration: Felling &amp; Rigging Crew Member</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stream-restoration-felling--rigging-crew-member-chattanooga-tennessee/4618527876</t>
+  </si>
+  <si>
+    <t>Volunteer Engagement Assistant</t>
+  </si>
+  <si>
+    <t>Colorado Parks And Wildlife</t>
+  </si>
+  <si>
+    <t>$20 - $21 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-volunteer-engagement-assistant-denver-colorado/5072391036</t>
+  </si>
+  <si>
+    <t>Volunteer Resource Development Specialist</t>
+  </si>
+  <si>
+    <t>$20 - $22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-volunteer-resource-development-specialist-denver-colorado/2942932838</t>
+  </si>
+  <si>
+    <t>Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>Redding, CA</t>
+  </si>
+  <si>
+    <t>$6,488 - $12,152 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-redding-california/5462714533</t>
+  </si>
+  <si>
+    <t>Water Systems Assistant Operator I/II – Environmental Services Department</t>
+  </si>
+  <si>
+    <t>City of San Jose Environmental Services Department</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>$78,707.20 - $103,105.60 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-systems-assistant-operator-iii--environmental-services-department-san-jose-california/9031214527</t>
+  </si>
+  <si>
+    <t>Wetland Engineering Technician</t>
+  </si>
+  <si>
+    <t>Conservation Districts of Iowa</t>
+  </si>
+  <si>
+    <t>Charles City, IA</t>
+  </si>
+  <si>
+    <t>$18.47 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetland-engineering-technician-charles-city-iowa/5624912036</t>
+  </si>
+  <si>
+    <t>Wildlife Habitat Biologist - Fort Morgan, CO</t>
+  </si>
+  <si>
+    <t>Bird Conservancy of the Rockies</t>
+  </si>
+  <si>
+    <t>Fort Morgan, CO</t>
+  </si>
+  <si>
+    <t>$58,000 - $67,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-habitat-biologist-fort-morgan-colorado/8651994827</t>
+  </si>
+  <si>
+    <t>Wildlife Habitat Biologist - Hugo, CO</t>
+  </si>
+  <si>
+    <t>Hugo, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-habitat-biologist-hugo-colorado/1115306453</t>
+  </si>
+  <si>
+    <t>Wildlife Management Specialist</t>
+  </si>
+  <si>
+    <t>Panora, IA</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>ecology-forestry-general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-management-specialist-panora-iowa/3724255938</t>
+  </si>
+  <si>
+    <t>Accountant (remote)</t>
+  </si>
+  <si>
+    <t>Fohrman &amp; Fohrman, Inc.</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/bb339aa34dfb4844a96d37723033cc02-accountant-remote-fohrman-fohrman-inc-dana-point</t>
+  </si>
+  <si>
+    <t>Accounts Manager</t>
+  </si>
+  <si>
+    <t>Animal Aid Unlimited</t>
+  </si>
+  <si>
+    <t>Udaipur, RJ, IN</t>
+  </si>
+  <si>
+    <t>INR 70000.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a8a49ca924a41f69a47f315dbf8409b-accounts-manager-animal-aid-unlimited-udaipur</t>
+  </si>
+  <si>
+    <t>Activity Specialist: Art (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3625dcd3e50641ba9aa06f7e7e710212-activity-specialist-art-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Activity Specialist: Fitness &amp; Nutrition (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff5f1345cad34fe59f15f35c8c96bc12-activity-specialist-fitness-nutrition-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Activity Specialist: STEM (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b50d0c84573484ea4981d1d2166a66f-activity-specialist-stem-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Administrative Assistant I (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/395185a32e2e47329b1ca3925900dcfb-administrative-assistant-i-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Bridges Baltimore</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0aee221223c341a3b081391197d530ae-administrative-coordinator-bridges-baltimore-baltimore</t>
+  </si>
+  <si>
+    <t>Damariscotta, Maine</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>Conservation Job Board</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99579973b82c448097131c509ce84e75-advancement-director-coastal-rivers-conservation-trust-damariscotta</t>
+  </si>
+  <si>
+    <t>Advocacy Counsel (Mid-Level or Senior-Level)</t>
+  </si>
+  <si>
+    <t>International Corporate Accountability Roundtable</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b092955cea764f11bbb6a1ce7dc805fa-advocacy-counsel-mid-level-or-senior-level-international-corporate-accountability-roundtable-washington</t>
+  </si>
+  <si>
+    <t>Affordable Housing Preservation Staff Attorney</t>
+  </si>
+  <si>
+    <t>Massachusetts Law Reform Institute (MLRI)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Environment, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1cf129e742b419d835f1f421e29e80a-affordable-housing-preservation-staff-attorney-massachusetts-law-reform-institute-mlri-boston</t>
+  </si>
+  <si>
+    <t>Asistentes de asignación de becas</t>
+  </si>
+  <si>
+    <t>Fundación Cimientos (español)</t>
+  </si>
+  <si>
+    <t>Buenos Aires, C, AR</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9329e42d9173419387de2c675ac1389d-asistentes-de-asignacion-de-becas-fundacion-cimientos-espanol-buenos-aires</t>
+  </si>
+  <si>
+    <t>Assistant Director, Community Engagement &amp; Leadership</t>
+  </si>
+  <si>
+    <t>Brandeis University</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 63400.00 - 75400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1de0eaa247c40f18259fe6bb5a83358-assistant-director-community-engagement-leadership-brandeis-university-waltham</t>
+  </si>
+  <si>
+    <t>Associate Director of Programs &amp; Services</t>
+  </si>
+  <si>
+    <t>BAGLY Inc.</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a024f85b6b724ec1bdcc783ec737e6d4-associate-director-of-programs-services-bagly-inc-boston</t>
+  </si>
+  <si>
+    <t>Better Builder Coordinator</t>
+  </si>
+  <si>
+    <t>Workers Defense Action Fund</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c5718c3ce024fa39164f81d40fe19f2-better-builder-coordinator-workers-defense-action-fund-austin</t>
+  </si>
+  <si>
+    <t>Chief Commercial Lending and Operations Officer</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2166109660224168ab72260b5bdbc881-chief-commercial-lending-and-operations-officer-neighborworks-affiliates-washington</t>
+  </si>
+  <si>
+    <t>Chief of Staff - New York State Assembly District 34</t>
+  </si>
+  <si>
+    <t>Brian for NY</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba17a2e1ba3248ed9f641f0c74091ff0-chief-of-staff-new-york-state-assembly-district-34-brian-for-ny-queens-county</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>IWS Family Health</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5114a2c76d05413eb3567f041bfaeb1a-chief-operating-officer-iws-family-health-chicago</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9612fea7719c4b3493224829dc05d353-communications-manager-bridges-baltimore-baltimore</t>
+  </si>
+  <si>
+    <t>Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>Guide Dogs of the Desert</t>
+  </si>
+  <si>
+    <t>Whitewater, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 70304.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea4d5cfe0075481d83e69c4f8a6a3f6a-community-engagement-manager-guide-dogs-of-the-desert-whitewater</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>VOCAL-NY</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 58795.89 - 68295.89/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b3aaac705564a3a87aedc0351992cfc-community-organizer-vocal-ny-rochester</t>
+  </si>
+  <si>
+    <t>Community-Based PHN 10 Nurse Coordinator</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>USD 1666.71 - 2345.20/week</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53c226c4d60c438f99d688e3935e9eb5-community-based-phn-10-nurse-coordinator-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Conservation Grants Associate (Latin America)</t>
+  </si>
+  <si>
+    <t>Rainforest Trust</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fe44db6fd704346a3ffa43f2f66cdf5-conservation-grants-associate-latin-america-rainforest-trust-warrenton</t>
+  </si>
+  <si>
+    <t>CTUL Lead Organizer (Bilingual English/Spanish)</t>
+  </si>
+  <si>
+    <t>Centro de Trabajadores Unidos En Lucha (CTUL)</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 77250.00 - 77250.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d4cd3767fd1434e9358e73a08db5cc1-ctul-lead-organizer-bilingual-englishspanish-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
+    <t>Development Specialist</t>
+  </si>
+  <si>
+    <t>International OCD Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7437fe97589d409481df5ede3753617e-development-specialist-international-ocd-foundation-boston</t>
+  </si>
+  <si>
+    <t>Director of Civic Engagement</t>
+  </si>
+  <si>
+    <t>Leaders for Educational Advocacy and Diversity (LEAD)</t>
+  </si>
+  <si>
+    <t>Danbury, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ec4fd843a5049a58b8d721f08a932b3-director-of-civic-engagement-leaders-for-educational-advocacy-and-diversity-lead-danbury</t>
+  </si>
+  <si>
+    <t>Director of Sports &amp; Fitness</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6defbf4da5a1404985456efe9b91d5f9-director-of-sports-fitness-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Director, Impact and Innovation</t>
+  </si>
+  <si>
+    <t>American Public Human Services Association</t>
+  </si>
+  <si>
+    <t>USD 112000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbbc9874e0794bf78f0b5a37cfceaef6-director-impact-and-innovation-american-public-human-services-association-arlington</t>
+  </si>
+  <si>
+    <t>Education Advocate, Immigrant Students' Rights Project</t>
+  </si>
+  <si>
+    <t>Advocates for Children of New York, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 62489.00 - 68003.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/519f15195d1e4ba5ba2ac346a760c5b1-education-advocate-immigrant-students-rights-project-advocates-for-children-of-new-york-inc-new-york</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>Global Village Project</t>
+  </si>
+  <si>
+    <t>Decatur, Georgia</t>
+  </si>
+  <si>
+    <t>USD 43000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a502f6e6ccc94617bc54794334b414c9-education-coordinator-global-village-project-decatur</t>
+  </si>
+  <si>
+    <t>BloomAgainBklyn, Inc.</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 95000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0559393cd00042e383a01f1552b7e166-executive-director-bloomagainbklyn-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Executive Director of People and Culture</t>
+  </si>
+  <si>
+    <t>Vivalon</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Seniors Retirement, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5050192183ad4fd48a8b98efbe49c479-executive-director-of-people-and-culture-vivalon-san-rafael</t>
+  </si>
+  <si>
+    <t>Facilities Supervisor</t>
+  </si>
+  <si>
+    <t>Union Settlement Association</t>
+  </si>
+  <si>
+    <t>USD 60500.00 - 60500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c0e2a0bd7284db5b13dc25df2b3dd3d-facilities-supervisor-union-settlement-association-new-york</t>
+  </si>
+  <si>
+    <t>Front Desk &amp; Office Coordinator</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e8b409367a6409480cdb37d52612559-front-desk-office-coordinator-massachusetts-law-reform-institute-mlri-boston</t>
+  </si>
+  <si>
+    <t>Fundraising &amp; Communications Coordinator</t>
+  </si>
+  <si>
+    <t>BDP Impact Real Estate</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b7e8330d50b547dd9994ca8da9d48bd8-fundraising-communications-coordinator-bdp-impact-real-estate-philadelphia</t>
+  </si>
+  <si>
+    <t>GENDER-BASED VIOLENCE SPECIALIST</t>
+  </si>
+  <si>
+    <t>Family Violence Law Center</t>
+  </si>
+  <si>
+    <t>USD 35.90 - 35.90/hour</t>
+  </si>
+  <si>
+    <t>Victim Support, Crime Safety, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79e224e8aadf42bf92cf119f40874e3f-gender-based-violence-specialist-family-violence-law-center-oakland</t>
+  </si>
+  <si>
+    <t>Grants Program Specialist</t>
+  </si>
+  <si>
+    <t>Farm and Food Growth Fund, Inc</t>
+  </si>
+  <si>
+    <t>Hudson, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4aa32e871b644633b10a0a1094628e12-grants-program-specialist-farm-and-food-growth-fund-inc-hudson</t>
+  </si>
+  <si>
+    <t>Immigration / Immigrant Rights Litigation Sr. Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50ab43bd7d2747588bdf40c90e5bcdd7-immigration-immigrant-rights-litigation-sr-staff-attorney-massachusetts-law-reform-institute-mlri-boston</t>
+  </si>
+  <si>
+    <t>IMMIGRATION LAW ATTORNEY (Worcester)</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/344a9d35ad5f46a1a741e7952ef466f3-immigration-law-attorney-worcester-community-legal-aid-affiliate-worcester</t>
+  </si>
+  <si>
+    <t>Inclusion Specialist (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>USD 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbcf90f9cc974af6899d396b23328986-inclusion-specialist-castle-hill-ymca-ymca-of-greater-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Individual and Major Giving Director</t>
+  </si>
+  <si>
+    <t>Encore Community Services</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2284ae68a0874e4da805d0cc25de8994-individual-and-major-giving-director-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>INVESTIGADOR</t>
+  </si>
+  <si>
+    <t>Asociación Civil Anti Bullying Argentina</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5d8451e996a4ea9be293e7fbf3e555a-investigador-asociacion-civil-anti-bullying-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Legal Assistant</t>
+  </si>
+  <si>
+    <t>USD 63702.00 - 69323.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa87c97605254ed29e5aad7b2ecd4b13-legal-assistant-advocates-for-children-of-new-york-inc-new-york</t>
+  </si>
+  <si>
+    <t>Líder de Tecnologia, Dados e Processos</t>
+  </si>
+  <si>
+    <t>Instituto Semear</t>
+  </si>
+  <si>
+    <t>Remote (BR)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/073a9b1122784f25b3e9ac6778550ed5-lider-de-tecnologia-dados-e-processos-instituto-semear-sao-paulo</t>
+  </si>
+  <si>
+    <t>Managing Director - International Nonprofit Institute</t>
+  </si>
+  <si>
+    <t>Dietrich W. Botstiber Foundation</t>
+  </si>
+  <si>
+    <t>Media, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Animals, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16a67d5f58a042238195b667d298110a-managing-director-international-nonprofit-institute-dietrich-w-botstiber-foundation-media</t>
+  </si>
+  <si>
+    <t>Middle School Spanish Teacher</t>
+  </si>
+  <si>
+    <t>Two Rivers Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 66173.00 - 106668.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7333fbe3d49e43d3b7d4200a498916f8-middle-school-spanish-teacher-two-rivers-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>MLRI Senior Economic Attorney</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 122000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de5af4c6b5c74d86b6b077cdca6074c7-mlri-senior-economic-attorney-massachusetts-law-reform-institute-mlri-boston</t>
+  </si>
+  <si>
+    <t>Multi-Region Infant &amp; Early Childhood Mental Health (IECMH) Consultant</t>
+  </si>
+  <si>
+    <t>Oregon Infant Mental Health Association</t>
+  </si>
+  <si>
+    <t>Salem, Oregon</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a3335aec9a944c386d4a105bc1cd868-multi-region-infant-early-childhood-mental-health-iecmh-consultant-oregon-infant-mental-health-association-salem</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Bang on a Can, Inc</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf16cb74d9e8413bb5bdf08db3f74b59-operations-manager-bang-on-a-can-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Paralegal A</t>
+  </si>
+  <si>
+    <t>Texas RioGrande Legal Aid, Inc. (TRLA)</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 44340.00 - 58403.96/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7e3872232454195a311decc86d691b8-paralegal-a-texas-riogrande-legal-aid-inc-trla-nashville</t>
+  </si>
+  <si>
+    <t>Part-Time Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Girl Vow, Inc.</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/429784ef99b4427fb5efdf4a237edd65-part-time-administrative-assistant-girl-vow-inc-new-york</t>
+  </si>
+  <si>
+    <t>Pathways Career Coach</t>
+  </si>
+  <si>
+    <t>Friends of the Children - National</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/588829ea4d074f89966ee496c6a02d7d-pathways-career-coach-friends-of-the-children-national-portland</t>
+  </si>
+  <si>
+    <t>President &amp; CEO</t>
+  </si>
+  <si>
+    <t>FIND Food Bank</t>
+  </si>
+  <si>
+    <t>Indio, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7f127477b7fc4066987131c6c62c3936-president-ceo-find-food-bank-indio</t>
+  </si>
+  <si>
+    <t>Program Support Coordinator (part-time)</t>
+  </si>
+  <si>
+    <t>Playtime Project</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3dd401e0ef1d4fca95b56316d49a1e3f-program-support-coordinator-part-time-playtime-project-washington</t>
+  </si>
+  <si>
+    <t>Project Leader</t>
+  </si>
+  <si>
+    <t>The Honeycomb Project</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/075a943913e9465ab2b06cfd257c209c-project-leader-the-honeycomb-project-washington</t>
+  </si>
+  <si>
+    <t>Project Manager, Advancement</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 85500.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d262c602eaa48cbb340111f08d75e02-project-manager-advancement-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>PT/Hybrid Development Manager</t>
+  </si>
+  <si>
+    <t>Integrative Communities dba The Social Impact Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Crime Safety, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4deb2ac6bccc410bb5bd82fe0fa84f85-pthybrid-development-manager-integrative-communities-dba-the-social-impact-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Publications Program Specialist</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Job Workplace, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/dcb7782c150d4ae5bc2c0bf3237b9d38-publications-program-specialist-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Regional Development Director</t>
+  </si>
+  <si>
+    <t>10,000 Degrees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c0ed582afac24e8c84b438e522daf3ea-regional-development-director-10000-degrees-san-rafael</t>
+  </si>
+  <si>
+    <t>Research Analyst - Carnegie California</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>Palo Alto, California</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e60c5e87c374d829ca5a67e902790ac-research-analyst-carnegie-california-carnegie-endowment-for-international-peace-palo-alto</t>
+  </si>
+  <si>
+    <t>Responsable de Administración</t>
+  </si>
+  <si>
+    <t>Fundación Nordelta</t>
+  </si>
+  <si>
+    <t>Rincón de Milberg, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>USD 2700000.00 - 3200000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e0e451c8c82746448c03d924adf10f28-responsable-de-administracion-fundacion-nordelta-rincon-de-milberg</t>
+  </si>
+  <si>
+    <t>Social Care Network Lead/Warehouse Worker</t>
+  </si>
+  <si>
+    <t>Metropolitan Council on Jewish Poverty</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5ba67908c6a49839b4706a6584f1fba-social-care-network-leadwarehouse-worker-metropolitan-council-on-jewish-poverty-new-york</t>
+  </si>
+  <si>
+    <t>Social Media Strategist</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2d7aa19e4e045bc9850fedea62e90bb-social-media-strategist-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/044198158a5c47b78a0c51c2dc7715ba-social-media-strategist-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>Sr. Content Strategist</t>
+  </si>
+  <si>
+    <t>PixelSpoke</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1c912166d59b467ea2f8b26541b2c950-sr-content-strategist-pixelspoke-wayne</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Louisiana Fair Housing Action Center</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90eb4c2a3ece4ef5a3533d8d57d3e56b-staff-attorney-louisiana-fair-housing-action-center-new-orleans</t>
+  </si>
+  <si>
+    <t>Staff Paralegal for Nonprofit Law Firm</t>
+  </si>
+  <si>
+    <t>Mass Deportation Defense</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c74b6627b4c947c39d24d21a57560db0-staff-paralegal-for-nonprofit-law-firm-mass-deportation-defense-boston</t>
+  </si>
+  <si>
+    <t>Strategic Advisor to the CEO</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/418f36d326584b61839d4637f9b15f6c-strategic-advisor-to-the-ceo-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>Supervising Attorney, Manhattan Team</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34938276fd174568a993d360daf113c2-supervising-attorney-manhattan-team-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Technology Coordinator (Bard High School Early College Manhattan)</t>
+  </si>
+  <si>
+    <t>Bard Early Colleges</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7b75b19c6a74b9eb2d79cebce9fa48f-technology-coordinator-bard-high-school-early-college-manhattan-bard-early-colleges-new-york</t>
+  </si>
+  <si>
+    <t>Vice President, Philanthropic Advising</t>
+  </si>
+  <si>
+    <t>Third Plateau</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/0512f809a8c14e73bf938cbe2b25ce92-vice-president-philanthropic-advising-third-plateau-san-francisco</t>
+  </si>
+  <si>
+    <t>Worker Organizer</t>
+  </si>
+  <si>
+    <t>USD 61500.00 - 63500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c855f2243e5c4f16bee5074bf97b2bd8-worker-organizer-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1725,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1751,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2133,1117 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>155</v>
+      </c>
+      <c r="F30" t="s">
+        <v>156</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32" t="s">
+        <v>115</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="s">
+        <v>138</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" t="s">
+        <v>156</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>188</v>
+      </c>
+      <c r="F38" t="s">
+        <v>189</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" t="s">
+        <v>192</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" t="s">
+        <v>195</v>
+      </c>
+      <c r="C41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" t="s">
+        <v>199</v>
+      </c>
+      <c r="F41" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>210</v>
+      </c>
+      <c r="B44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>213</v>
+      </c>
+      <c r="F44" t="s">
+        <v>192</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>218</v>
+      </c>
+      <c r="F45" t="s">
+        <v>219</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>221</v>
+      </c>
+      <c r="B46" t="s">
+        <v>216</v>
+      </c>
+      <c r="C46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>218</v>
+      </c>
+      <c r="F46" t="s">
+        <v>219</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>226</v>
+      </c>
+      <c r="F47" t="s">
+        <v>227</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3299,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3338,1717 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" t="s">
+        <v>247</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" t="s">
+        <v>247</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F8" t="s">
+        <v>260</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" t="s">
+        <v>270</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F11" t="s">
+        <v>275</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" t="s">
+        <v>281</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C14" t="s">
+        <v>290</v>
+      </c>
+      <c r="D14" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" t="s">
+        <v>291</v>
+      </c>
+      <c r="F14" t="s">
+        <v>292</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C15" t="s">
+        <v>296</v>
+      </c>
+      <c r="D15" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" t="s">
+        <v>297</v>
+      </c>
+      <c r="F15" t="s">
+        <v>298</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>300</v>
+      </c>
+      <c r="B16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" t="s">
+        <v>303</v>
+      </c>
+      <c r="F16" t="s">
+        <v>304</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>306</v>
+      </c>
+      <c r="B17" t="s">
+        <v>307</v>
+      </c>
+      <c r="C17" t="s">
+        <v>308</v>
+      </c>
+      <c r="D17" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" t="s">
+        <v>309</v>
+      </c>
+      <c r="F17" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18" t="s">
+        <v>313</v>
+      </c>
+      <c r="D18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" t="s">
+        <v>315</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E19" t="s">
+        <v>318</v>
+      </c>
+      <c r="F19" t="s">
+        <v>260</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" t="s">
+        <v>324</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" t="s">
+        <v>329</v>
+      </c>
+      <c r="F21" t="s">
+        <v>234</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>331</v>
+      </c>
+      <c r="B22" t="s">
+        <v>332</v>
+      </c>
+      <c r="C22" t="s">
+        <v>290</v>
+      </c>
+      <c r="D22" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" t="s">
+        <v>333</v>
+      </c>
+      <c r="F22" t="s">
+        <v>334</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" t="s">
+        <v>338</v>
+      </c>
+      <c r="F23" t="s">
+        <v>339</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>341</v>
+      </c>
+      <c r="B24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C24" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" t="s">
+        <v>345</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" t="s">
+        <v>348</v>
+      </c>
+      <c r="C25" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" t="s">
+        <v>232</v>
+      </c>
+      <c r="E25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F25" t="s">
+        <v>350</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>352</v>
+      </c>
+      <c r="B26" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" t="s">
+        <v>354</v>
+      </c>
+      <c r="D26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F26" t="s">
+        <v>356</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>358</v>
+      </c>
+      <c r="B27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" t="s">
+        <v>360</v>
+      </c>
+      <c r="F27" t="s">
+        <v>361</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>363</v>
+      </c>
+      <c r="B28" t="s">
+        <v>364</v>
+      </c>
+      <c r="C28" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" t="s">
+        <v>365</v>
+      </c>
+      <c r="F28" t="s">
+        <v>366</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>368</v>
+      </c>
+      <c r="B29" t="s">
+        <v>369</v>
+      </c>
+      <c r="C29" t="s">
+        <v>370</v>
+      </c>
+      <c r="D29" t="s">
+        <v>232</v>
+      </c>
+      <c r="E29" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" t="s">
+        <v>372</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>374</v>
+      </c>
+      <c r="B30" t="s">
+        <v>375</v>
+      </c>
+      <c r="C30" t="s">
+        <v>376</v>
+      </c>
+      <c r="D30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" t="s">
+        <v>377</v>
+      </c>
+      <c r="F30" t="s">
+        <v>378</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" t="s">
+        <v>383</v>
+      </c>
+      <c r="F31" t="s">
+        <v>384</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>386</v>
+      </c>
+      <c r="B32" t="s">
+        <v>387</v>
+      </c>
+      <c r="C32" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E32" t="s">
+        <v>389</v>
+      </c>
+      <c r="F32" t="s">
+        <v>390</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>392</v>
+      </c>
+      <c r="B33" t="s">
+        <v>393</v>
+      </c>
+      <c r="C33" t="s">
+        <v>370</v>
+      </c>
+      <c r="D33" t="s">
+        <v>232</v>
+      </c>
+      <c r="E33" t="s">
+        <v>394</v>
+      </c>
+      <c r="F33" t="s">
+        <v>395</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>397</v>
+      </c>
+      <c r="B34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" t="s">
+        <v>290</v>
+      </c>
+      <c r="D34" t="s">
+        <v>245</v>
+      </c>
+      <c r="E34" t="s">
+        <v>234</v>
+      </c>
+      <c r="F34" t="s">
+        <v>398</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>400</v>
+      </c>
+      <c r="B35" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" t="s">
+        <v>231</v>
+      </c>
+      <c r="D35" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" t="s">
+        <v>360</v>
+      </c>
+      <c r="F35" t="s">
+        <v>402</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>404</v>
+      </c>
+      <c r="B36" t="s">
+        <v>405</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" t="s">
+        <v>232</v>
+      </c>
+      <c r="E36" t="s">
+        <v>406</v>
+      </c>
+      <c r="F36" t="s">
+        <v>407</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>409</v>
+      </c>
+      <c r="B37" t="s">
+        <v>410</v>
+      </c>
+      <c r="C37" t="s">
+        <v>411</v>
+      </c>
+      <c r="D37" t="s">
+        <v>232</v>
+      </c>
+      <c r="E37" t="s">
+        <v>412</v>
+      </c>
+      <c r="F37" t="s">
+        <v>413</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>415</v>
+      </c>
+      <c r="B38" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" t="s">
+        <v>416</v>
+      </c>
+      <c r="F38" t="s">
+        <v>417</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>419</v>
+      </c>
+      <c r="B39" t="s">
+        <v>420</v>
+      </c>
+      <c r="C39" t="s">
+        <v>421</v>
+      </c>
+      <c r="D39" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" t="s">
+        <v>422</v>
+      </c>
+      <c r="F39" t="s">
+        <v>423</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>425</v>
+      </c>
+      <c r="B40" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" t="s">
+        <v>426</v>
+      </c>
+      <c r="F40" t="s">
+        <v>247</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>428</v>
+      </c>
+      <c r="B41" t="s">
+        <v>429</v>
+      </c>
+      <c r="C41" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" t="s">
+        <v>431</v>
+      </c>
+      <c r="F41" t="s">
+        <v>432</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>434</v>
+      </c>
+      <c r="B42" t="s">
+        <v>435</v>
+      </c>
+      <c r="C42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D42" t="s">
+        <v>382</v>
+      </c>
+      <c r="E42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F42" t="s">
+        <v>436</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>438</v>
+      </c>
+      <c r="B43" t="s">
+        <v>369</v>
+      </c>
+      <c r="C43" t="s">
+        <v>370</v>
+      </c>
+      <c r="D43" t="s">
+        <v>232</v>
+      </c>
+      <c r="E43" t="s">
+        <v>439</v>
+      </c>
+      <c r="F43" t="s">
+        <v>372</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>441</v>
+      </c>
+      <c r="B44" t="s">
+        <v>442</v>
+      </c>
+      <c r="C44" t="s">
+        <v>443</v>
+      </c>
+      <c r="D44" t="s">
+        <v>382</v>
+      </c>
+      <c r="E44" t="s">
+        <v>234</v>
+      </c>
+      <c r="F44" t="s">
+        <v>281</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>445</v>
+      </c>
+      <c r="B45" t="s">
+        <v>446</v>
+      </c>
+      <c r="C45" t="s">
+        <v>447</v>
+      </c>
+      <c r="D45" t="s">
+        <v>232</v>
+      </c>
+      <c r="E45" t="s">
+        <v>234</v>
+      </c>
+      <c r="F45" t="s">
+        <v>448</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>450</v>
+      </c>
+      <c r="B46" t="s">
+        <v>451</v>
+      </c>
+      <c r="C46" t="s">
+        <v>302</v>
+      </c>
+      <c r="D46" t="s">
+        <v>232</v>
+      </c>
+      <c r="E46" t="s">
+        <v>452</v>
+      </c>
+      <c r="F46" t="s">
+        <v>378</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>454</v>
+      </c>
+      <c r="B47" t="s">
+        <v>273</v>
+      </c>
+      <c r="C47" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" t="s">
+        <v>455</v>
+      </c>
+      <c r="F47" t="s">
+        <v>417</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>457</v>
+      </c>
+      <c r="B48" t="s">
+        <v>458</v>
+      </c>
+      <c r="C48" t="s">
+        <v>459</v>
+      </c>
+      <c r="D48" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" t="s">
+        <v>460</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>462</v>
+      </c>
+      <c r="B49" t="s">
+        <v>463</v>
+      </c>
+      <c r="C49" t="s">
+        <v>464</v>
+      </c>
+      <c r="D49" t="s">
+        <v>232</v>
+      </c>
+      <c r="E49" t="s">
+        <v>465</v>
+      </c>
+      <c r="F49" t="s">
+        <v>466</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>468</v>
+      </c>
+      <c r="B50" t="s">
+        <v>469</v>
+      </c>
+      <c r="C50" t="s">
+        <v>470</v>
+      </c>
+      <c r="D50" t="s">
+        <v>232</v>
+      </c>
+      <c r="E50" t="s">
+        <v>471</v>
+      </c>
+      <c r="F50" t="s">
+        <v>472</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>474</v>
+      </c>
+      <c r="B51" t="s">
+        <v>475</v>
+      </c>
+      <c r="C51" t="s">
+        <v>430</v>
+      </c>
+      <c r="D51" t="s">
+        <v>232</v>
+      </c>
+      <c r="E51" t="s">
+        <v>476</v>
+      </c>
+      <c r="F51" t="s">
+        <v>260</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>478</v>
+      </c>
+      <c r="B52" t="s">
+        <v>479</v>
+      </c>
+      <c r="C52" t="s">
+        <v>480</v>
+      </c>
+      <c r="D52" t="s">
+        <v>232</v>
+      </c>
+      <c r="E52" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" t="s">
+        <v>395</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>482</v>
+      </c>
+      <c r="B53" t="s">
+        <v>483</v>
+      </c>
+      <c r="C53" t="s">
+        <v>484</v>
+      </c>
+      <c r="D53" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" t="s">
+        <v>234</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>486</v>
+      </c>
+      <c r="B54" t="s">
+        <v>487</v>
+      </c>
+      <c r="C54" t="s">
+        <v>302</v>
+      </c>
+      <c r="D54" t="s">
+        <v>245</v>
+      </c>
+      <c r="E54" t="s">
+        <v>488</v>
+      </c>
+      <c r="F54" t="s">
+        <v>460</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>490</v>
+      </c>
+      <c r="B55" t="s">
+        <v>491</v>
+      </c>
+      <c r="C55" t="s">
+        <v>302</v>
+      </c>
+      <c r="D55" t="s">
+        <v>382</v>
+      </c>
+      <c r="E55" t="s">
+        <v>234</v>
+      </c>
+      <c r="F55" t="s">
+        <v>492</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>494</v>
+      </c>
+      <c r="B56" t="s">
+        <v>495</v>
+      </c>
+      <c r="C56" t="s">
+        <v>496</v>
+      </c>
+      <c r="D56" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" t="s">
+        <v>497</v>
+      </c>
+      <c r="F56" t="s">
+        <v>498</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>500</v>
+      </c>
+      <c r="B57" t="s">
+        <v>501</v>
+      </c>
+      <c r="C57" t="s">
+        <v>502</v>
+      </c>
+      <c r="D57" t="s">
+        <v>245</v>
+      </c>
+      <c r="E57" t="s">
+        <v>503</v>
+      </c>
+      <c r="F57" t="s">
+        <v>504</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>506</v>
+      </c>
+      <c r="B58" t="s">
+        <v>507</v>
+      </c>
+      <c r="C58" t="s">
+        <v>508</v>
+      </c>
+      <c r="D58" t="s">
+        <v>280</v>
+      </c>
+      <c r="E58" t="s">
+        <v>509</v>
+      </c>
+      <c r="F58" t="s">
+        <v>510</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>512</v>
+      </c>
+      <c r="B59" t="s">
+        <v>513</v>
+      </c>
+      <c r="C59" t="s">
+        <v>388</v>
+      </c>
+      <c r="D59" t="s">
+        <v>232</v>
+      </c>
+      <c r="E59" t="s">
+        <v>234</v>
+      </c>
+      <c r="F59" t="s">
+        <v>234</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>515</v>
+      </c>
+      <c r="B60" t="s">
+        <v>516</v>
+      </c>
+      <c r="C60" t="s">
+        <v>517</v>
+      </c>
+      <c r="D60" t="s">
+        <v>232</v>
+      </c>
+      <c r="E60" t="s">
+        <v>318</v>
+      </c>
+      <c r="F60" t="s">
+        <v>518</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>520</v>
+      </c>
+      <c r="B61" t="s">
+        <v>521</v>
+      </c>
+      <c r="C61" t="s">
+        <v>522</v>
+      </c>
+      <c r="D61" t="s">
+        <v>232</v>
+      </c>
+      <c r="E61" t="s">
+        <v>523</v>
+      </c>
+      <c r="F61" t="s">
+        <v>524</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>526</v>
+      </c>
+      <c r="B62" t="s">
+        <v>527</v>
+      </c>
+      <c r="C62" t="s">
+        <v>370</v>
+      </c>
+      <c r="D62" t="s">
+        <v>232</v>
+      </c>
+      <c r="E62" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" t="s">
+        <v>528</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>530</v>
+      </c>
+      <c r="B63" t="s">
+        <v>531</v>
+      </c>
+      <c r="C63" t="s">
+        <v>370</v>
+      </c>
+      <c r="D63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E63" t="s">
+        <v>234</v>
+      </c>
+      <c r="F63" t="s">
+        <v>356</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>530</v>
+      </c>
+      <c r="B64" t="s">
+        <v>531</v>
+      </c>
+      <c r="C64" t="s">
+        <v>302</v>
+      </c>
+      <c r="D64" t="s">
+        <v>232</v>
+      </c>
+      <c r="E64" t="s">
+        <v>234</v>
+      </c>
+      <c r="F64" t="s">
+        <v>356</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>534</v>
+      </c>
+      <c r="B65" t="s">
+        <v>535</v>
+      </c>
+      <c r="C65" t="s">
+        <v>231</v>
+      </c>
+      <c r="D65" t="s">
+        <v>232</v>
+      </c>
+      <c r="E65" t="s">
+        <v>234</v>
+      </c>
+      <c r="F65" t="s">
+        <v>234</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>537</v>
+      </c>
+      <c r="B66" t="s">
+        <v>538</v>
+      </c>
+      <c r="C66" t="s">
+        <v>539</v>
+      </c>
+      <c r="D66" t="s">
+        <v>232</v>
+      </c>
+      <c r="E66" t="s">
+        <v>349</v>
+      </c>
+      <c r="F66" t="s">
+        <v>234</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>541</v>
+      </c>
+      <c r="B67" t="s">
+        <v>542</v>
+      </c>
+      <c r="C67" t="s">
+        <v>40</v>
+      </c>
+      <c r="D67" t="s">
+        <v>232</v>
+      </c>
+      <c r="E67" t="s">
+        <v>297</v>
+      </c>
+      <c r="F67" t="s">
+        <v>543</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>545</v>
+      </c>
+      <c r="B68" t="s">
+        <v>429</v>
+      </c>
+      <c r="C68" t="s">
+        <v>370</v>
+      </c>
+      <c r="D68" t="s">
+        <v>232</v>
+      </c>
+      <c r="E68" t="s">
+        <v>546</v>
+      </c>
+      <c r="F68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>549</v>
+      </c>
+      <c r="B69" t="s">
+        <v>550</v>
+      </c>
+      <c r="C69" t="s">
+        <v>370</v>
+      </c>
+      <c r="D69" t="s">
+        <v>232</v>
+      </c>
+      <c r="E69" t="s">
+        <v>234</v>
+      </c>
+      <c r="F69" t="s">
+        <v>551</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>553</v>
+      </c>
+      <c r="B70" t="s">
+        <v>554</v>
+      </c>
+      <c r="C70" t="s">
+        <v>370</v>
+      </c>
+      <c r="D70" t="s">
+        <v>232</v>
+      </c>
+      <c r="E70" t="s">
+        <v>555</v>
+      </c>
+      <c r="F70" t="s">
+        <v>556</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>558</v>
+      </c>
+      <c r="B71" t="s">
+        <v>559</v>
+      </c>
+      <c r="C71" t="s">
+        <v>231</v>
+      </c>
+      <c r="D71" t="s">
+        <v>232</v>
+      </c>
+      <c r="E71" t="s">
+        <v>234</v>
+      </c>
+      <c r="F71" t="s">
+        <v>560</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>562</v>
+      </c>
+      <c r="B72" t="s">
+        <v>342</v>
+      </c>
+      <c r="C72" t="s">
+        <v>343</v>
+      </c>
+      <c r="D72" t="s">
+        <v>232</v>
+      </c>
+      <c r="E72" t="s">
+        <v>563</v>
+      </c>
+      <c r="F72" t="s">
+        <v>345</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-22.xlsx
+++ b/docs/xlsx/jobs-2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="937">
   <si>
     <t>Title</t>
   </si>
@@ -703,6 +703,27 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-management-specialist-panora-iowa/3724255938</t>
   </si>
   <si>
+    <t>Water Resources Regulatory Specialist</t>
+  </si>
+  <si>
+    <t>Capitol Region Watershed District</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>60,000 - 80,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/water-resources-regulatory-specialist/</t>
+  </si>
+  <si>
     <t>Accountant (remote)</t>
   </si>
   <si>
@@ -724,6 +745,24 @@
     <t>https://www.idealist.org/en/consultant-job/bb339aa34dfb4844a96d37723033cc02-accountant-remote-fohrman-fohrman-inc-dana-point</t>
   </si>
   <si>
+    <t>Accounting Associate</t>
+  </si>
+  <si>
+    <t>RESOLVE</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8457dc3446d4a0e8fdce12b5178b3bd-accounting-associate-resolve-washington</t>
+  </si>
+  <si>
     <t>Accounts Manager</t>
   </si>
   <si>
@@ -865,6 +904,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9329e42d9173419387de2c675ac1389d-asistentes-de-asignacion-de-becas-fundacion-cimientos-espanol-buenos-aires</t>
   </si>
   <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/7f613704b7244e0a9be10da5b5fef1a1-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/79b3b95b08b740499b103230caf3e7c5-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
     <t>Assistant Director, Community Engagement &amp; Leadership</t>
   </si>
   <si>
@@ -880,15 +937,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/c1de0eaa247c40f18259fe6bb5a83358-assistant-director-community-engagement-leadership-brandeis-university-waltham</t>
   </si>
   <si>
+    <t>Associate Director of Individual Giving</t>
+  </si>
+  <si>
+    <t>American Kidney Fund</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a2dc5baa40f46c9955cb3b0c36e4960-associate-director-of-individual-giving-american-kidney-fund-rockville</t>
+  </si>
+  <si>
     <t>Associate Director of Programs &amp; Services</t>
   </si>
   <si>
     <t>BAGLY Inc.</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -922,9 +994,6 @@
     <t>NeighborWorks Affiliates</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 140000.00 - 160000.00/year</t>
   </si>
   <si>
@@ -934,6 +1003,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2166109660224168ab72260b5bdbc881-chief-commercial-lending-and-operations-officer-neighborworks-affiliates-washington</t>
   </si>
   <si>
+    <t>Chief Marketing and Communications Officer</t>
+  </si>
+  <si>
+    <t>Family Promise</t>
+  </si>
+  <si>
+    <t>USD 170000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb573ac016284ec98c7cb479a02da1d6-chief-marketing-and-communications-officer-family-promise-summit</t>
+  </si>
+  <si>
     <t>Chief of Staff - New York State Assembly District 34</t>
   </si>
   <si>
@@ -967,6 +1051,78 @@
     <t>https://www.idealist.org/en/nonprofit-job/5114a2c76d05413eb3567f041bfaeb1a-chief-operating-officer-iws-family-health-chicago</t>
   </si>
   <si>
+    <t>Chief, Finance and Operations</t>
+  </si>
+  <si>
+    <t>Baltimore's Promise</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b57550ad511f43659562cc4c067402f5-chief-finance-and-operations-baltimores-promise-baltimore</t>
+  </si>
+  <si>
+    <t>Church Administrator, part-time 15 hours per week</t>
+  </si>
+  <si>
+    <t>Connexion UME</t>
+  </si>
+  <si>
+    <t>Somerville, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59135eee46bf48eda18e0086127a6642-church-administrator-part-time-15-hours-per-week-connexion-ume-somerville</t>
+  </si>
+  <si>
+    <t>Client Success Manager (Salesforce)</t>
+  </si>
+  <si>
+    <t>Craftsman Technology Group</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2c578011c0ec45899181cd7c85d800b1-client-success-manager-salesforce-craftsman-technology-group-boston</t>
+  </si>
+  <si>
+    <t>Coastal Advocate – MID COAST</t>
+  </si>
+  <si>
+    <t>One Hundred Miles</t>
+  </si>
+  <si>
+    <t>Darien, Georgia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/647d0765ba98447bb36e59e3c106bb93-coastal-advocate-mid-coast-one-hundred-miles-darien</t>
+  </si>
+  <si>
+    <t>Coastal Planning and Policy Strategist</t>
+  </si>
+  <si>
+    <t>Savannah, Georgia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3b42cc2199c44edba3cb56c35bc8aff-coastal-planning-and-policy-strategist-one-hundred-miles-savannah</t>
+  </si>
+  <si>
     <t>Communications Manager</t>
   </si>
   <si>
@@ -994,6 +1150,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ea4d5cfe0075481d83e69c4f8a6a3f6a-community-engagement-manager-guide-dogs-of-the-desert-whitewater</t>
   </si>
   <si>
+    <t>Community Manager</t>
+  </si>
+  <si>
+    <t>Diabetes Foundation</t>
+  </si>
+  <si>
+    <t>Mahwah, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a155138ed994a9f81f001fc0db668be-community-manager-diabetes-foundation-mahwah</t>
+  </si>
+  <si>
     <t>Community Organizer</t>
   </si>
   <si>
@@ -1009,6 +1183,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/8b3aaac705564a3a87aedc0351992cfc-community-organizer-vocal-ny-rochester</t>
   </si>
   <si>
+    <t>Community Organizing Supervisor</t>
+  </si>
+  <si>
+    <t>Center For Disability Rights</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b029802430a47099aaf889163ddc871-community-organizing-supervisor-center-for-disability-rights-rochester</t>
+  </si>
+  <si>
     <t>Community-Based PHN 10 Nurse Coordinator</t>
   </si>
   <si>
@@ -1024,6 +1213,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/53c226c4d60c438f99d688e3935e9eb5-community-based-phn-10-nurse-coordinator-boston-public-health-commission-boston</t>
   </si>
   <si>
+    <t>ConfiKids Development Director - Build the Future of ConfiKids‍</t>
+  </si>
+  <si>
+    <t>ConfiKids</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Philanthropy, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6f29dfe05d64dab9c78f9323daf5ace-confikids-development-director-build-the-future-of-confikids-confikids-foxborough</t>
+  </si>
+  <si>
     <t>Conservation Grants Associate (Latin America)</t>
   </si>
   <si>
@@ -1057,6 +1264,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/6d4cd3767fd1434e9358e73a08db5cc1-ctul-lead-organizer-bilingual-englishspanish-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
   </si>
   <si>
+    <t>Data Analytics Associate</t>
+  </si>
+  <si>
+    <t>Tipping Point Community</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 93600.00 - 93600.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d4f78cad9734272943d358d0989071d-data-analytics-associate-tipping-point-community-san-francisco</t>
+  </si>
+  <si>
+    <t>Data Assistant</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e4d5af613394f5dbb522f435dc808cd-data-assistant-diabetes-foundation-mahwah</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>ROOM: A Sketchbook for Analytic Action</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 70.00 - 100.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Media, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20d52b9517a841928397cccaf7dc727b-development-communications-manager-room-a-sketchbook-for-analytic-action-new-york</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>National Nordic Museum</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/118794b45cc740e58b484c7b61be6945-development-coordinator-national-nordic-museum-seattle</t>
+  </si>
+  <si>
+    <t>Development Operations Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51adf7e606e945c591085289d6e6aa14-development-operations-associate-tipping-point-community-san-francisco</t>
+  </si>
+  <si>
     <t>Development Specialist</t>
   </si>
   <si>
@@ -1072,6 +1345,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7437fe97589d409481df5ede3753617e-development-specialist-international-ocd-foundation-boston</t>
   </si>
   <si>
+    <t>DIETITIAN, PART TIME</t>
+  </si>
+  <si>
+    <t>Meals on Wheels People, Inc.</t>
+  </si>
+  <si>
+    <t>USD 34.50 - 40.50/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99101f25337344909be62d5206eb8264-dietitian-part-time-meals-on-wheels-people-inc-portland</t>
+  </si>
+  <si>
     <t>Director of Civic Engagement</t>
   </si>
   <si>
@@ -1090,6 +1378,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ec4fd843a5049a58b8d721f08a932b3-director-of-civic-engagement-leaders-for-educational-advocacy-and-diversity-lead-danbury</t>
   </si>
   <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Lift To Rise</t>
+  </si>
+  <si>
+    <t>Palm Desert, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d19c6db3eae4a3f9221921a0eea64da-director-of-communications-lift-to-rise-palm-desert</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>OSG</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a9e3071200c47938d1e0488b7352e60-director-of-development-osg-arlington</t>
+  </si>
+  <si>
+    <t>Director of Operations and Analytics</t>
+  </si>
+  <si>
+    <t>California Center for Movement Legal Services</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1af097c379a047cfbcf19919abe4ded0-director-of-operations-and-analytics-california-center-for-movement-legal-services-oakland</t>
+  </si>
+  <si>
     <t>Director of Sports &amp; Fitness</t>
   </si>
   <si>
@@ -1105,6 +1447,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6defbf4da5a1404985456efe9b91d5f9-director-of-sports-fitness-west-end-house-boston</t>
   </si>
   <si>
+    <t>Director, Development &amp; Communications</t>
+  </si>
+  <si>
+    <t>Westchester Children's Association</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df8cbf8c64064398a56c77ad56fdb373-director-development-communications-westchester-childrens-association-white-plains</t>
+  </si>
+  <si>
     <t>Director, Impact and Innovation</t>
   </si>
   <si>
@@ -1120,6 +1477,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/fbbc9874e0794bf78f0b5a37cfceaef6-director-impact-and-innovation-american-public-human-services-association-arlington</t>
   </si>
   <si>
+    <t>Director, Youth &amp; Family (Long Island City YMCA)</t>
+  </si>
+  <si>
+    <t>Queens, New York</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a82c5bca5e374a3693a33bfb41b52ecd-director-youth-family-long-island-city-ymca-ymca-of-greater-new-york-queens</t>
+  </si>
+  <si>
     <t>Education Advocate, Immigrant Students' Rights Project</t>
   </si>
   <si>
@@ -1162,9 +1531,6 @@
     <t>Brooklyn, New York</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 95000.00/year</t>
   </si>
   <si>
@@ -1174,6 +1540,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/0559393cd00042e383a01f1552b7e166-executive-director-bloomagainbklyn-inc-brooklyn</t>
   </si>
   <si>
+    <t>Loaves &amp; Fishes Food Pantry</t>
+  </si>
+  <si>
+    <t>Ellsworth, Maine</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d2a8b509b7a4a9a85dc24b554713c6e-executive-director-loaves-fishes-food-pantry-ellsworth</t>
+  </si>
+  <si>
     <t>Executive Director of People and Culture</t>
   </si>
   <si>
@@ -1192,6 +1570,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/5050192183ad4fd48a8b98efbe49c479-executive-director-of-people-and-culture-vivalon-san-rafael</t>
   </si>
   <si>
+    <t>Executive Director, Congo Initiative USA</t>
+  </si>
+  <si>
+    <t>Congo Initiative</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b276c0891814882960ab623ebf8867c-executive-director-congo-initiative-usa-congo-initiative-raleigh</t>
+  </si>
+  <si>
     <t>Facilities Supervisor</t>
   </si>
   <si>
@@ -1207,6 +1597,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/0c0e2a0bd7284db5b13dc25df2b3dd3d-facilities-supervisor-union-settlement-association-new-york</t>
   </si>
   <si>
+    <t>Financial Controller</t>
+  </si>
+  <si>
+    <t>Civilization Research Institute</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e71a906e5c8143a9abce6480c59852b7-financial-controller-civilization-research-institute-asheville</t>
+  </si>
+  <si>
     <t>Front Desk &amp; Office Coordinator</t>
   </si>
   <si>
@@ -1243,6 +1645,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/79e224e8aadf42bf92cf119f40874e3f-gender-based-violence-specialist-family-violence-law-center-oakland</t>
   </si>
   <si>
+    <t>Grant Project Manager (Temporary)</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3e73d5c7f8314df59037594dbb9cc575-grant-project-manager-temporary-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Grants Program Specialist</t>
   </si>
   <si>
@@ -1252,15 +1666,54 @@
     <t>Hudson, New York</t>
   </si>
   <si>
-    <t>USD 50000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>Agriculture, Community Development, Economic Development</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4aa32e871b644633b10a0a1094628e12-grants-program-specialist-farm-and-food-growth-fund-inc-hudson</t>
   </si>
   <si>
+    <t>HR Generalist</t>
+  </si>
+  <si>
+    <t>Museum of History &amp; Industry (MOHAI)</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 41.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/269aea52fbb6478e80beb40f41c4ab4b-hr-generalist-museum-of-history-industry-mohai-seattle</t>
+  </si>
+  <si>
+    <t>Human Resources Consultant</t>
+  </si>
+  <si>
+    <t>Abortion Fund of Maryland</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 30000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09bb13937a9849da85266075ecd97d08-human-resources-consultant-abortion-fund-of-maryland-baltimore</t>
+  </si>
+  <si>
+    <t>Hutch Kids Executive Director</t>
+  </si>
+  <si>
+    <t>Hutch Kids Child Care Center</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37f469007fe0401bad790010fa9fc95e-hutch-kids-executive-director-hutch-kids-child-care-center-seattle</t>
+  </si>
+  <si>
     <t>Immigration / Immigrant Rights Litigation Sr. Staff Attorney</t>
   </si>
   <si>
@@ -1318,6 +1771,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2284ae68a0874e4da805d0cc25de8994-individual-and-major-giving-director-encore-community-services-new-york</t>
   </si>
   <si>
+    <t>Integration Consultant - Salesforce &amp; Grantmaking Systems</t>
+  </si>
+  <si>
+    <t>Sertus Partners</t>
+  </si>
+  <si>
+    <t>USD 110.00 - 110.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy, Science Technology, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/de7030d0561e4e0488d03c3f35211c33-integration-consultant-salesforce-grantmaking-systems-sertus-partners-montclair</t>
+  </si>
+  <si>
     <t>INVESTIGADOR</t>
   </si>
   <si>
@@ -1330,6 +1798,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/b5d8451e996a4ea9be293e7fbf3e555a-investigador-asociacion-civil-anti-bullying-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Lead Engineer</t>
+  </si>
+  <si>
+    <t>Jacobson Consulting Applications</t>
+  </si>
+  <si>
+    <t>USD 100750.00 - 111400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6480694b5e9f4de5b1bd024c4d3fc28d-lead-engineer-jacobson-consulting-applications-chicago</t>
+  </si>
+  <si>
     <t>Legal Assistant</t>
   </si>
   <si>
@@ -1396,27 +1876,84 @@
     <t>Salem, Oregon</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/8a3335aec9a944c386d4a105bc1cd868-multi-region-infant-early-childhood-mental-health-iecmh-consultant-oregon-infant-mental-health-association-salem</t>
   </si>
   <si>
+    <t>Now Recruiting PAID Mentors | MCIP Afterschool Mentoring Initiative (Washington, DC)</t>
+  </si>
+  <si>
+    <t>Multicultural Career Intern Program</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d26fcf0259046c78fbf5c525c3e26ab-now-recruiting-paid-mentors-mcip-afterschool-mentoring-initiative-washington-dc-multicultural-career-intern-program-washington</t>
+  </si>
+  <si>
+    <t>Ocean Staff Attorney (Term-Limited)</t>
+  </si>
+  <si>
+    <t>The Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/167fdb9c2a8748dc98c3ea9595030ed6-ocean-staff-attorney-term-limited-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Colorado Trust</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 37.00 - 44.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a96463aaada54400a87ebcc18aac1d59-office-manager-colorado-trust-denver</t>
+  </si>
+  <si>
+    <t>OMH Clinical Supervisor - Evening/Weekend</t>
+  </si>
+  <si>
+    <t>Bridging Access To Care Inc</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6754c8f6f2f94d24845fe43ceba33a8c-omh-clinical-supervisor-eveningweekend-bridging-access-to-care-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Operations and Analytics Coordinator</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13c6281734f6468db0f88f60c9fb1a03-operations-and-analytics-coordinator-california-center-for-movement-legal-services-oakland</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
     <t>Bang on a Can, Inc</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 60000.00/year</t>
   </si>
   <si>
-    <t>Arts Music</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/cf16cb74d9e8413bb5bdf08db3f74b59-operations-manager-bang-on-a-can-inc-kings-county</t>
   </si>
   <si>
@@ -1450,6 +1987,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/429784ef99b4427fb5efdf4a237edd65-part-time-administrative-assistant-girl-vow-inc-new-york</t>
   </si>
   <si>
+    <t>Part-Time STEAM Instructor</t>
+  </si>
+  <si>
+    <t>Young STEAMers</t>
+  </si>
+  <si>
+    <t>Union City, California</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f9cf452c54540029f3585c6f4b4cb5c-part-time-steam-instructor-young-steamers-union-city</t>
+  </si>
+  <si>
     <t>Pathways Career Coach</t>
   </si>
   <si>
@@ -1537,9 +2092,6 @@
     <t>Publications Program Specialist</t>
   </si>
   <si>
-    <t>The Choice Inc</t>
-  </si>
-  <si>
     <t>Remote (District of Columbia)</t>
   </si>
   <si>
@@ -1639,6 +2191,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/90eb4c2a3ece4ef5a3533d8d57d3e56b-staff-attorney-louisiana-fair-housing-action-center-new-orleans</t>
   </si>
   <si>
+    <t>Staff Attorney - Homelessness Prevention (Affirmative Litigation)</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67b595dab6034871b1bd933c561095b9-staff-attorney-homelessness-prevention-affirmative-litigation-public-counsel-los-angeles</t>
+  </si>
+  <si>
     <t>Staff Paralegal for Nonprofit Law Firm</t>
   </si>
   <si>
@@ -1663,15 +2233,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/418f36d326584b61839d4637f9b15f6c-strategic-advisor-to-the-ceo-encore-community-services-new-york</t>
   </si>
   <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Legal Aid Bureau, Inc.</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09d6d776488d43a9a0d3688dcab8a4af-supervising-attorney-legal-aid-bureau-inc-rockville</t>
+  </si>
+  <si>
     <t>Supervising Attorney, Manhattan Team</t>
   </si>
   <si>
     <t>New York Legal Assistance Group (NYLAG)</t>
   </si>
   <si>
-    <t>Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/34938276fd174568a993d360daf113c2-supervising-attorney-manhattan-team-new-york-legal-assistance-group-nylag-new-york</t>
   </si>
   <si>
@@ -1690,6 +2272,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/d7b75b19c6a74b9eb2d79cebce9fa48f-technology-coordinator-bard-high-school-early-college-manhattan-bard-early-colleges-new-york</t>
   </si>
   <si>
+    <t>Trainer, Integrated Safety Planning</t>
+  </si>
+  <si>
+    <t>Zero Overdose Corporation</t>
+  </si>
+  <si>
+    <t>USD 75.00 - 150.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15d173ccf7e440f9a40f9af25db3c89d-trainer-integrated-safety-planning-zero-overdose-corporation-new-york</t>
+  </si>
+  <si>
+    <t>Trauma Therapist- (Full-time)</t>
+  </si>
+  <si>
+    <t>Partnerships for Trauma Recovery</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2580610ec76644fea4128d50b18fbf23-trauma-therapist-full-time-partnerships-for-trauma-recovery-berkeley</t>
+  </si>
+  <si>
     <t>Vice President, Philanthropic Advising</t>
   </si>
   <si>
@@ -1709,6 +2324,507 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/c855f2243e5c4f16bee5074bf97b2bd8-worker-organizer-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
+    <t>Workforce Coordinator</t>
+  </si>
+  <si>
+    <t>Pennsylvania Coalition for Oral Health</t>
+  </si>
+  <si>
+    <t>Remote (Pennsylvania)</t>
+  </si>
+  <si>
+    <t>USD 62400.00 - 62400.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b8c4df849eb48f887f30b4d183affa8-workforce-coordinator-pennsylvania-coalition-for-oral-health-mechanicsburg</t>
+  </si>
+  <si>
+    <t>AGRONOMY AND PRODUCER ENGAGEMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>SASKATCHEWAN - Collective Impact</t>
+  </si>
+  <si>
+    <t>Not Stated, Saskatchewan</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73368559</t>
+  </si>
+  <si>
+    <t>ASSISTANT DIRECTOR</t>
+  </si>
+  <si>
+    <t>GRASSROOTS AND POLITICAL ENGAGEMENT - American Farm Bureau Federation</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73353895</t>
+  </si>
+  <si>
+    <t>ASSOCIATE DIRECTOR</t>
+  </si>
+  <si>
+    <t>FOOD POLICY PROGRAM - Campaign for Tobacco Free Kids</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73356339</t>
+  </si>
+  <si>
+    <t>STATE GOVERNMENT RELATIONS - Share Our Strength</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73358783</t>
+  </si>
+  <si>
+    <t>CAMPAIGN SPECIALIST</t>
+  </si>
+  <si>
+    <t>New Roots Institute</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73378335</t>
+  </si>
+  <si>
+    <t>COMMUNITY LEADERSHIP AND ENGAGEMENT ORGANIZER</t>
+  </si>
+  <si>
+    <t>Syracuse Onodaga Food Systems Alliance</t>
+  </si>
+  <si>
+    <t>Onondaga County, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73361227</t>
+  </si>
+  <si>
+    <t>COOK</t>
+  </si>
+  <si>
+    <t>Community Servings</t>
+  </si>
+  <si>
+    <t>Jamaica Plain, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73367337</t>
+  </si>
+  <si>
+    <t>DATA SCIENTIST</t>
+  </si>
+  <si>
+    <t>USDA</t>
+  </si>
+  <si>
+    <t>Location Options: Little Rock, AR, Fort Collins, C</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73360005</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF LENDING</t>
+  </si>
+  <si>
+    <t>Berkshire Agricultural Ventures</t>
+  </si>
+  <si>
+    <t>Great Barrington, Massachusetts</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73362449</t>
+  </si>
+  <si>
+    <t>DISASTER FEEDING PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>IDEA</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73352673</t>
+  </si>
+  <si>
+    <t>EHS SPECIALIST</t>
+  </si>
+  <si>
+    <t>CENTER OF EXCELLENCE IPM - University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Davis, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73388111</t>
+  </si>
+  <si>
+    <t>ELKUS RANCH REC DIRECTOR</t>
+  </si>
+  <si>
+    <t>University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Half Moon Bay, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73385667</t>
+  </si>
+  <si>
+    <t>EVALUATION AND TRIALS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Seed Savers Exchange</t>
+  </si>
+  <si>
+    <t>Decorah, Iowa</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73373447</t>
+  </si>
+  <si>
+    <t>EXECUTIVE ASSISTANT TO THE SENIOR VICE PRESIDENT AND SENIOR ASSOCIATE FOOD AGRICULTURE AND NATURAL RESOURCES</t>
+  </si>
+  <si>
+    <t>Association of Public and Land Grant Universities</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73374669</t>
+  </si>
+  <si>
+    <t>EXTENSION EDUCATOR</t>
+  </si>
+  <si>
+    <t>AGRICULTURE AND FOOD SYSTEMS - University of Maryland Extension</t>
+  </si>
+  <si>
+    <t>Talbot County, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73382001</t>
+  </si>
+  <si>
+    <t>FACILITIES MANAGER</t>
+  </si>
+  <si>
+    <t>Center for an Agricultural Economy</t>
+  </si>
+  <si>
+    <t>Hardwick, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73389333</t>
+  </si>
+  <si>
+    <t>FACULTY SPECIALIST AND PROGRAM DIRECTOR, AGRICULTURAL NUTRIENT MANAGEMENT PROGRAM</t>
+  </si>
+  <si>
+    <t>University of Maryland Extension</t>
+  </si>
+  <si>
+    <t>College Park, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73383223</t>
+  </si>
+  <si>
+    <t>FARM KITCHEN AND MARKETING COORDINATOR</t>
+  </si>
+  <si>
+    <t>Resource Cleveland</t>
+  </si>
+  <si>
+    <t>Cleveland, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73369781</t>
+  </si>
+  <si>
+    <t>FARMER SUPPORT SPECIALIST</t>
+  </si>
+  <si>
+    <t>Community Alliance with Family Farmers</t>
+  </si>
+  <si>
+    <t>Based in or adjacent to one of these counties: Sac</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73384445</t>
+  </si>
+  <si>
+    <t>FOOD PANTRY COORDINATOR</t>
+  </si>
+  <si>
+    <t>State Center Community College District</t>
+  </si>
+  <si>
+    <t>Districtwide, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73379557</t>
+  </si>
+  <si>
+    <t>FOOD SOURCING COORDINATOR</t>
+  </si>
+  <si>
+    <t>Mid Ohio Food Collective</t>
+  </si>
+  <si>
+    <t>Grove City, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73344119</t>
+  </si>
+  <si>
+    <t>LEAD</t>
+  </si>
+  <si>
+    <t>SNAP - National Council on Aging</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73355117</t>
+  </si>
+  <si>
+    <t>LEGISLATIVE ASSISTANT FOR AGRICULTURE AND WATER</t>
+  </si>
+  <si>
+    <t>Office of US Senator Adam Schiff</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73375891</t>
+  </si>
+  <si>
+    <t>MANAGER OF GOVERNMENT AFFAIRS AND PUBLIC AFFAIRS</t>
+  </si>
+  <si>
+    <t>Tillamook County Creamery Association</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73372225</t>
+  </si>
+  <si>
+    <t>MARKETING AND PROMOTIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>Pacific Coast Farmers Market Association</t>
+  </si>
+  <si>
+    <t>Concord, California</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73390555</t>
+  </si>
+  <si>
+    <t>MARKETING SERVICES COORDINATOR</t>
+  </si>
+  <si>
+    <t>A Greener World</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73347785</t>
+  </si>
+  <si>
+    <t>MEMBERSHIP RELATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>MANRRS</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73394221</t>
+  </si>
+  <si>
+    <t>OUTREACH SPECIALIST</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73346563</t>
+  </si>
+  <si>
+    <t>PACKING ASSOCIATE</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73366115</t>
+  </si>
+  <si>
+    <t>PHD RESEARCH ASSISTANTSHIP</t>
+  </si>
+  <si>
+    <t>GROWING SUSTAINABLE FOOD SYSTEMS - Kansas State University</t>
+  </si>
+  <si>
+    <t>Olathe, Kansas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73357561</t>
+  </si>
+  <si>
+    <t>PRESIDENT AND CEO</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73345341</t>
+  </si>
+  <si>
+    <t>PROFESSOR OF THE PRACTICE IN FOOD SYSTEMS</t>
+  </si>
+  <si>
+    <t>Tufts University</t>
+  </si>
+  <si>
+    <t>Medford, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73391777</t>
+  </si>
+  <si>
+    <t>PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>FOOD PANTRY - Sentara Health</t>
+  </si>
+  <si>
+    <t>Woodbridge, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73350229</t>
+  </si>
+  <si>
+    <t>PRODUCE MARKETPLACE - Mon Valley Initiative</t>
+  </si>
+  <si>
+    <t>Homestead, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73351451</t>
+  </si>
+  <si>
+    <t>PROJECT COMMUNICATIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>The Ohio State University</t>
+  </si>
+  <si>
+    <t>Wooster, Ohio</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73377113</t>
+  </si>
+  <si>
+    <t>REGIONAL LIVESTOCK EDUCATOR</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>LaCrosse, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73392999</t>
+  </si>
+  <si>
+    <t>SLAUGHTER SPECIALIST</t>
+  </si>
+  <si>
+    <t>FARM AUDITOR - A Greener World</t>
+  </si>
+  <si>
+    <t>Remote with extensive travel in US and Canada, Rem</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73349007</t>
+  </si>
+  <si>
+    <t>SUPERVISORY SOIL CONSERVATIONIST</t>
+  </si>
+  <si>
+    <t>ASSISTANT STATE CONSERVATIONIST FOR FIELD OPERATIONS - NRCS - USDA</t>
+  </si>
+  <si>
+    <t>Missoula, Montana</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73395443</t>
+  </si>
+  <si>
+    <t>SUSTAINABILITY PROGRAM LEAD</t>
+  </si>
+  <si>
+    <t>Farmers Business Network</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73380779</t>
+  </si>
+  <si>
+    <t>SUSTAINABILITY PROJECT MANAGER</t>
+  </si>
+  <si>
+    <t>VALUE CHAIN - Agropur</t>
+  </si>
+  <si>
+    <t>Eden Prairie, MN or Appleton, WI, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73371003</t>
+  </si>
+  <si>
+    <t>TEACHING KITCHEN PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73363671</t>
+  </si>
+  <si>
+    <t>UC COOPERATIVE EXTENSION VERTEBRATE PEST MANAGEMENT AREA ADVISOR</t>
+  </si>
+  <si>
+    <t>TREE FIELD AND VEGETABLE CROPS SERVING CALIFORNIAS SAN JOAQUIN VALLEY - University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Five Points, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73386889</t>
+  </si>
+  <si>
+    <t>VOLUNTEER COORDINATOR</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73364893</t>
+  </si>
+  <si>
+    <t>VOLUNTEER OPERATIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73342897</t>
   </si>
 </sst>
 </file>
@@ -3251,7 +4367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3290,8 +4406,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3299,7 +4441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3340,945 +4482,945 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C2" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F2" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E5" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E6" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F6" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F7" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" t="s">
         <v>256</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>257</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>258</v>
       </c>
-      <c r="D8" t="s">
-        <v>232</v>
-      </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F8" t="s">
         <v>260</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>269</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>270</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E9" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E10" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F10" t="s">
-        <v>270</v>
+        <v>277</v>
+      </c>
+      <c r="G10" t="s">
+        <v>278</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>238</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F11" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="E12" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="F12" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B13" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="E13" t="s">
-        <v>286</v>
+        <v>241</v>
       </c>
       <c r="F13" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C14" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F14" t="s">
-        <v>292</v>
+        <v>241</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F15" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C16" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F16" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D17" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F17" t="s">
-        <v>234</v>
+        <v>311</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C18" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F18" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>320</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F19" t="s">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B20" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C20" t="s">
-        <v>322</v>
+        <v>245</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E20" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F20" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B21" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C21" t="s">
-        <v>328</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F21" t="s">
-        <v>234</v>
+        <v>332</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B22" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C22" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F22" t="s">
-        <v>334</v>
+        <v>241</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B23" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>341</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E23" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F23" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B24" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C24" t="s">
-        <v>343</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E24" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F24" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B25" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C25" t="s">
-        <v>290</v>
+        <v>352</v>
       </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="E25" t="s">
-        <v>349</v>
+        <v>259</v>
       </c>
       <c r="F25" t="s">
-        <v>350</v>
+        <v>241</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>238</v>
       </c>
       <c r="D26" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E26" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F26" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B27" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C27" t="s">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E27" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F27" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>365</v>
+      </c>
+      <c r="B28" t="s">
+        <v>360</v>
+      </c>
+      <c r="C28" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" t="s">
+        <v>367</v>
+      </c>
+      <c r="F28" t="s">
         <v>363</v>
       </c>
-      <c r="B28" t="s">
-        <v>364</v>
-      </c>
-      <c r="C28" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E28" t="s">
-        <v>365</v>
-      </c>
-      <c r="F28" t="s">
-        <v>366</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B29" t="s">
-        <v>369</v>
+        <v>270</v>
       </c>
       <c r="C29" t="s">
+        <v>271</v>
+      </c>
+      <c r="D29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" t="s">
         <v>370</v>
       </c>
-      <c r="D29" t="s">
-        <v>232</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>273</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="F29" t="s">
-        <v>372</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>372</v>
+      </c>
+      <c r="B30" t="s">
+        <v>373</v>
+      </c>
+      <c r="C30" t="s">
         <v>374</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E30" t="s">
         <v>375</v>
       </c>
-      <c r="C30" t="s">
+      <c r="F30" t="s">
         <v>376</v>
       </c>
-      <c r="D30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="H30" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="F30" t="s">
-        <v>378</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="B31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" t="s">
         <v>380</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
+        <v>258</v>
+      </c>
+      <c r="E31" t="s">
         <v>381</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>382</v>
       </c>
-      <c r="E31" t="s">
+      <c r="H31" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="F31" t="s">
-        <v>384</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>384</v>
+      </c>
+      <c r="B32" t="s">
+        <v>385</v>
+      </c>
+      <c r="C32" t="s">
         <v>386</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D32" t="s">
+        <v>239</v>
+      </c>
+      <c r="E32" t="s">
         <v>387</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
+        <v>241</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="D32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E32" t="s">
-        <v>389</v>
-      </c>
-      <c r="F32" t="s">
-        <v>390</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>389</v>
+      </c>
+      <c r="B33" t="s">
+        <v>390</v>
+      </c>
+      <c r="C33" t="s">
+        <v>386</v>
+      </c>
+      <c r="D33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" t="s">
+        <v>391</v>
+      </c>
+      <c r="F33" t="s">
         <v>392</v>
       </c>
-      <c r="B33" t="s">
+      <c r="H33" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C33" t="s">
-        <v>370</v>
-      </c>
-      <c r="D33" t="s">
-        <v>232</v>
-      </c>
-      <c r="E33" t="s">
-        <v>394</v>
-      </c>
-      <c r="F33" t="s">
-        <v>395</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>394</v>
+      </c>
+      <c r="B34" t="s">
+        <v>395</v>
+      </c>
+      <c r="C34" t="s">
+        <v>298</v>
+      </c>
+      <c r="D34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" t="s">
+        <v>396</v>
+      </c>
+      <c r="F34" t="s">
         <v>397</v>
       </c>
-      <c r="B34" t="s">
-        <v>273</v>
-      </c>
-      <c r="C34" t="s">
-        <v>290</v>
-      </c>
-      <c r="D34" t="s">
-        <v>245</v>
-      </c>
-      <c r="E34" t="s">
-        <v>234</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="H34" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>399</v>
+      </c>
+      <c r="B35" t="s">
         <v>400</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>401</v>
       </c>
-      <c r="C35" t="s">
-        <v>231</v>
-      </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="E35" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="F35" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B36" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E36" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F36" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B37" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C37" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D37" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E37" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F37" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B38" t="s">
-        <v>273</v>
+        <v>417</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>418</v>
       </c>
       <c r="D38" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E38" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F38" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B39" t="s">
-        <v>420</v>
+        <v>379</v>
       </c>
       <c r="C39" t="s">
-        <v>421</v>
+        <v>380</v>
       </c>
       <c r="D39" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E39" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="F39" t="s">
+        <v>311</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>424</v>
+      </c>
+      <c r="B40" t="s">
         <v>425</v>
       </c>
-      <c r="B40" t="s">
-        <v>243</v>
-      </c>
       <c r="C40" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D40" t="s">
-        <v>245</v>
+        <v>426</v>
       </c>
       <c r="E40" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F40" t="s">
-        <v>247</v>
+        <v>428</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B41" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C41" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E41" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F41" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B42" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C42" t="s">
-        <v>231</v>
+        <v>418</v>
       </c>
       <c r="D42" t="s">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="E42" t="s">
-        <v>234</v>
+        <v>419</v>
       </c>
       <c r="F42" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>437</v>
@@ -4289,689 +5431,1701 @@
         <v>438</v>
       </c>
       <c r="B43" t="s">
-        <v>369</v>
+        <v>439</v>
       </c>
       <c r="C43" t="s">
-        <v>370</v>
+        <v>298</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E43" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F43" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C44" t="s">
-        <v>443</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>382</v>
+        <v>258</v>
       </c>
       <c r="E44" t="s">
-        <v>234</v>
+        <v>445</v>
       </c>
       <c r="F44" t="s">
-        <v>281</v>
+        <v>446</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B45" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C45" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D45" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E45" t="s">
-        <v>234</v>
+        <v>451</v>
       </c>
       <c r="F45" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B46" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C46" t="s">
-        <v>302</v>
+        <v>456</v>
       </c>
       <c r="D46" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E46" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F46" t="s">
-        <v>378</v>
+        <v>458</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B47" t="s">
-        <v>273</v>
+        <v>461</v>
       </c>
       <c r="C47" t="s">
-        <v>40</v>
+        <v>462</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E47" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="F47" t="s">
-        <v>417</v>
+        <v>464</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="B48" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="C48" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E48" t="s">
-        <v>234</v>
+        <v>469</v>
       </c>
       <c r="F48" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="C49" t="s">
-        <v>464</v>
+        <v>298</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E49" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F49" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B50" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C50" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="D50" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E50" t="s">
-        <v>471</v>
+        <v>315</v>
       </c>
       <c r="F50" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B51" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C51" t="s">
-        <v>430</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E51" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F51" t="s">
-        <v>260</v>
+        <v>485</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B52" t="s">
-        <v>479</v>
+        <v>256</v>
       </c>
       <c r="C52" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E52" t="s">
-        <v>233</v>
+        <v>489</v>
       </c>
       <c r="F52" t="s">
-        <v>395</v>
+        <v>260</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="C53" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E53" t="s">
-        <v>234</v>
+        <v>494</v>
       </c>
       <c r="F53" t="s">
-        <v>234</v>
+        <v>495</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="C54" t="s">
-        <v>302</v>
+        <v>499</v>
       </c>
       <c r="D54" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E54" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="F54" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C55" t="s">
-        <v>302</v>
+        <v>504</v>
       </c>
       <c r="D55" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="E55" t="s">
-        <v>234</v>
+        <v>505</v>
       </c>
       <c r="F55" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="C56" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="D56" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E56" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="F56" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C57" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="D57" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E57" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F57" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C58" t="s">
-        <v>508</v>
+        <v>238</v>
       </c>
       <c r="D58" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="F58" t="s">
-        <v>510</v>
+        <v>273</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="B59" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C59" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="D59" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E59" t="s">
-        <v>234</v>
+        <v>524</v>
       </c>
       <c r="F59" t="s">
-        <v>234</v>
+        <v>525</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B60" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C60" t="s">
-        <v>517</v>
+        <v>238</v>
       </c>
       <c r="D60" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E60" t="s">
-        <v>318</v>
+        <v>241</v>
       </c>
       <c r="F60" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s">
-        <v>521</v>
+        <v>286</v>
       </c>
       <c r="C61" t="s">
-        <v>522</v>
+        <v>298</v>
       </c>
       <c r="D61" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="E61" t="s">
-        <v>523</v>
+        <v>241</v>
       </c>
       <c r="F61" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B62" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C62" t="s">
-        <v>370</v>
+        <v>238</v>
       </c>
       <c r="D62" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E62" t="s">
-        <v>254</v>
+        <v>474</v>
       </c>
       <c r="F62" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B63" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C63" t="s">
-        <v>370</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E63" t="s">
-        <v>234</v>
+        <v>540</v>
       </c>
       <c r="F63" t="s">
-        <v>356</v>
+        <v>541</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="B64" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C64" t="s">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="D64" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="E64" t="s">
-        <v>234</v>
+        <v>545</v>
       </c>
       <c r="F64" t="s">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="B65" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="C65" t="s">
-        <v>231</v>
+        <v>549</v>
       </c>
       <c r="D65" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E65" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="F65" t="s">
-        <v>234</v>
+        <v>550</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="B66" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="C66" t="s">
-        <v>539</v>
+        <v>432</v>
       </c>
       <c r="D66" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E66" t="s">
-        <v>349</v>
+        <v>554</v>
       </c>
       <c r="F66" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="B67" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="C67" t="s">
-        <v>40</v>
+        <v>238</v>
       </c>
       <c r="D67" t="s">
-        <v>232</v>
+        <v>426</v>
       </c>
       <c r="E67" t="s">
-        <v>297</v>
+        <v>558</v>
       </c>
       <c r="F67" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="B68" t="s">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="C68" t="s">
-        <v>370</v>
+        <v>432</v>
       </c>
       <c r="D68" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E68" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="F68" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="B69" t="s">
-        <v>550</v>
+        <v>286</v>
       </c>
       <c r="C69" t="s">
-        <v>370</v>
+        <v>40</v>
       </c>
       <c r="D69" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E69" t="s">
-        <v>234</v>
+        <v>567</v>
       </c>
       <c r="F69" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="B70" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C70" t="s">
-        <v>370</v>
+        <v>572</v>
       </c>
       <c r="D70" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E70" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="F70" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="B71" t="s">
-        <v>559</v>
+        <v>256</v>
       </c>
       <c r="C71" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="E71" t="s">
-        <v>234</v>
+        <v>577</v>
       </c>
       <c r="F71" t="s">
-        <v>560</v>
+        <v>260</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="B72" t="s">
-        <v>342</v>
+        <v>580</v>
       </c>
       <c r="C72" t="s">
-        <v>343</v>
+        <v>581</v>
       </c>
       <c r="D72" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E72" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="F72" t="s">
-        <v>345</v>
+        <v>583</v>
       </c>
       <c r="H72" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>585</v>
+      </c>
+      <c r="B73" t="s">
+        <v>586</v>
+      </c>
+      <c r="C73" t="s">
+        <v>238</v>
+      </c>
+      <c r="D73" t="s">
+        <v>426</v>
+      </c>
+      <c r="E73" t="s">
+        <v>587</v>
+      </c>
+      <c r="F73" t="s">
+        <v>588</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>590</v>
+      </c>
+      <c r="B74" t="s">
+        <v>591</v>
+      </c>
+      <c r="C74" t="s">
+        <v>238</v>
+      </c>
+      <c r="D74" t="s">
+        <v>426</v>
+      </c>
+      <c r="E74" t="s">
+        <v>241</v>
+      </c>
+      <c r="F74" t="s">
+        <v>592</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>594</v>
+      </c>
+      <c r="B75" t="s">
+        <v>595</v>
+      </c>
+      <c r="C75" t="s">
+        <v>238</v>
+      </c>
+      <c r="D75" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" t="s">
+        <v>596</v>
+      </c>
+      <c r="F75" t="s">
+        <v>434</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>598</v>
+      </c>
+      <c r="B76" t="s">
+        <v>492</v>
+      </c>
+      <c r="C76" t="s">
+        <v>493</v>
+      </c>
+      <c r="D76" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" t="s">
+        <v>599</v>
+      </c>
+      <c r="F76" t="s">
+        <v>495</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>601</v>
+      </c>
+      <c r="B77" t="s">
+        <v>602</v>
+      </c>
+      <c r="C77" t="s">
+        <v>603</v>
+      </c>
+      <c r="D77" t="s">
+        <v>426</v>
+      </c>
+      <c r="E77" t="s">
+        <v>241</v>
+      </c>
+      <c r="F77" t="s">
+        <v>294</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>605</v>
+      </c>
+      <c r="B78" t="s">
+        <v>606</v>
+      </c>
+      <c r="C78" t="s">
+        <v>607</v>
+      </c>
+      <c r="D78" t="s">
+        <v>239</v>
+      </c>
+      <c r="E78" t="s">
+        <v>241</v>
+      </c>
+      <c r="F78" t="s">
+        <v>608</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>610</v>
+      </c>
+      <c r="B79" t="s">
+        <v>611</v>
+      </c>
+      <c r="C79" t="s">
+        <v>245</v>
+      </c>
+      <c r="D79" t="s">
+        <v>239</v>
+      </c>
+      <c r="E79" t="s">
+        <v>612</v>
+      </c>
+      <c r="F79" t="s">
+        <v>501</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>614</v>
+      </c>
+      <c r="B80" t="s">
+        <v>286</v>
+      </c>
+      <c r="C80" t="s">
+        <v>40</v>
+      </c>
+      <c r="D80" t="s">
+        <v>239</v>
+      </c>
+      <c r="E80" t="s">
+        <v>615</v>
+      </c>
+      <c r="F80" t="s">
+        <v>568</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>617</v>
+      </c>
+      <c r="B81" t="s">
+        <v>618</v>
+      </c>
+      <c r="C81" t="s">
+        <v>619</v>
+      </c>
+      <c r="D81" t="s">
+        <v>239</v>
+      </c>
+      <c r="E81" t="s">
+        <v>241</v>
+      </c>
+      <c r="F81" t="s">
         <v>564</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>621</v>
+      </c>
+      <c r="B82" t="s">
+        <v>622</v>
+      </c>
+      <c r="C82" t="s">
+        <v>245</v>
+      </c>
+      <c r="D82" t="s">
+        <v>426</v>
+      </c>
+      <c r="E82" t="s">
+        <v>623</v>
+      </c>
+      <c r="F82" t="s">
+        <v>294</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>625</v>
+      </c>
+      <c r="B83" t="s">
+        <v>626</v>
+      </c>
+      <c r="C83" t="s">
+        <v>298</v>
+      </c>
+      <c r="D83" t="s">
+        <v>293</v>
+      </c>
+      <c r="E83" t="s">
+        <v>241</v>
+      </c>
+      <c r="F83" t="s">
+        <v>627</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>629</v>
+      </c>
+      <c r="B84" t="s">
+        <v>630</v>
+      </c>
+      <c r="C84" t="s">
+        <v>631</v>
+      </c>
+      <c r="D84" t="s">
+        <v>239</v>
+      </c>
+      <c r="E84" t="s">
+        <v>632</v>
+      </c>
+      <c r="F84" t="s">
+        <v>241</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>634</v>
+      </c>
+      <c r="B85" t="s">
+        <v>635</v>
+      </c>
+      <c r="C85" t="s">
+        <v>636</v>
+      </c>
+      <c r="D85" t="s">
+        <v>239</v>
+      </c>
+      <c r="E85" t="s">
+        <v>637</v>
+      </c>
+      <c r="F85" t="s">
+        <v>638</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>640</v>
+      </c>
+      <c r="B86" t="s">
+        <v>467</v>
+      </c>
+      <c r="C86" t="s">
+        <v>468</v>
+      </c>
+      <c r="D86" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86" t="s">
+        <v>641</v>
+      </c>
+      <c r="F86" t="s">
+        <v>470</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>643</v>
+      </c>
+      <c r="B87" t="s">
+        <v>644</v>
+      </c>
+      <c r="C87" t="s">
+        <v>636</v>
+      </c>
+      <c r="D87" t="s">
+        <v>239</v>
+      </c>
+      <c r="E87" t="s">
+        <v>645</v>
+      </c>
+      <c r="F87" t="s">
+        <v>434</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>647</v>
+      </c>
+      <c r="B88" t="s">
+        <v>648</v>
+      </c>
+      <c r="C88" t="s">
+        <v>649</v>
+      </c>
+      <c r="D88" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" t="s">
+        <v>650</v>
+      </c>
+      <c r="F88" t="s">
+        <v>651</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>653</v>
+      </c>
+      <c r="B89" t="s">
+        <v>654</v>
+      </c>
+      <c r="C89" t="s">
+        <v>581</v>
+      </c>
+      <c r="D89" t="s">
+        <v>239</v>
+      </c>
+      <c r="E89" t="s">
+        <v>655</v>
+      </c>
+      <c r="F89" t="s">
+        <v>273</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>657</v>
+      </c>
+      <c r="B90" t="s">
+        <v>658</v>
+      </c>
+      <c r="C90" t="s">
+        <v>659</v>
+      </c>
+      <c r="D90" t="s">
+        <v>258</v>
+      </c>
+      <c r="E90" t="s">
+        <v>660</v>
+      </c>
+      <c r="F90" t="s">
+        <v>661</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>663</v>
+      </c>
+      <c r="B91" t="s">
+        <v>664</v>
+      </c>
+      <c r="C91" t="s">
+        <v>665</v>
+      </c>
+      <c r="D91" t="s">
+        <v>239</v>
+      </c>
+      <c r="E91" t="s">
+        <v>240</v>
+      </c>
+      <c r="F91" t="s">
+        <v>525</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>667</v>
+      </c>
+      <c r="B92" t="s">
+        <v>668</v>
+      </c>
+      <c r="C92" t="s">
+        <v>669</v>
+      </c>
+      <c r="D92" t="s">
+        <v>239</v>
+      </c>
+      <c r="E92" t="s">
+        <v>241</v>
+      </c>
+      <c r="F92" t="s">
+        <v>241</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>671</v>
+      </c>
+      <c r="B93" t="s">
+        <v>672</v>
+      </c>
+      <c r="C93" t="s">
+        <v>245</v>
+      </c>
+      <c r="D93" t="s">
+        <v>258</v>
+      </c>
+      <c r="E93" t="s">
+        <v>673</v>
+      </c>
+      <c r="F93" t="s">
+        <v>564</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>675</v>
+      </c>
+      <c r="B94" t="s">
+        <v>676</v>
+      </c>
+      <c r="C94" t="s">
+        <v>245</v>
+      </c>
+      <c r="D94" t="s">
+        <v>426</v>
+      </c>
+      <c r="E94" t="s">
+        <v>241</v>
+      </c>
+      <c r="F94" t="s">
+        <v>677</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>679</v>
+      </c>
+      <c r="B95" t="s">
+        <v>680</v>
+      </c>
+      <c r="C95" t="s">
+        <v>681</v>
+      </c>
+      <c r="D95" t="s">
+        <v>239</v>
+      </c>
+      <c r="E95" t="s">
+        <v>682</v>
+      </c>
+      <c r="F95" t="s">
+        <v>683</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>685</v>
+      </c>
+      <c r="B96" t="s">
+        <v>686</v>
+      </c>
+      <c r="C96" t="s">
+        <v>687</v>
+      </c>
+      <c r="D96" t="s">
+        <v>258</v>
+      </c>
+      <c r="E96" t="s">
+        <v>688</v>
+      </c>
+      <c r="F96" t="s">
+        <v>689</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>691</v>
+      </c>
+      <c r="B97" t="s">
+        <v>544</v>
+      </c>
+      <c r="C97" t="s">
+        <v>692</v>
+      </c>
+      <c r="D97" t="s">
+        <v>293</v>
+      </c>
+      <c r="E97" t="s">
+        <v>693</v>
+      </c>
+      <c r="F97" t="s">
+        <v>694</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>696</v>
+      </c>
+      <c r="B98" t="s">
+        <v>697</v>
+      </c>
+      <c r="C98" t="s">
+        <v>514</v>
+      </c>
+      <c r="D98" t="s">
+        <v>239</v>
+      </c>
+      <c r="E98" t="s">
+        <v>241</v>
+      </c>
+      <c r="F98" t="s">
+        <v>241</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>699</v>
+      </c>
+      <c r="B99" t="s">
+        <v>700</v>
+      </c>
+      <c r="C99" t="s">
+        <v>701</v>
+      </c>
+      <c r="D99" t="s">
+        <v>239</v>
+      </c>
+      <c r="E99" t="s">
+        <v>370</v>
+      </c>
+      <c r="F99" t="s">
+        <v>702</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>704</v>
+      </c>
+      <c r="B100" t="s">
+        <v>705</v>
+      </c>
+      <c r="C100" t="s">
+        <v>706</v>
+      </c>
+      <c r="D100" t="s">
+        <v>239</v>
+      </c>
+      <c r="E100" t="s">
+        <v>707</v>
+      </c>
+      <c r="F100" t="s">
+        <v>708</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>710</v>
+      </c>
+      <c r="B101" t="s">
+        <v>711</v>
+      </c>
+      <c r="C101" t="s">
+        <v>493</v>
+      </c>
+      <c r="D101" t="s">
+        <v>239</v>
+      </c>
+      <c r="E101" t="s">
+        <v>267</v>
+      </c>
+      <c r="F101" t="s">
+        <v>712</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>714</v>
+      </c>
+      <c r="B102" t="s">
+        <v>715</v>
+      </c>
+      <c r="C102" t="s">
+        <v>493</v>
+      </c>
+      <c r="D102" t="s">
+        <v>239</v>
+      </c>
+      <c r="E102" t="s">
+        <v>241</v>
+      </c>
+      <c r="F102" t="s">
+        <v>452</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>714</v>
+      </c>
+      <c r="B103" t="s">
+        <v>715</v>
+      </c>
+      <c r="C103" t="s">
+        <v>245</v>
+      </c>
+      <c r="D103" t="s">
+        <v>239</v>
+      </c>
+      <c r="E103" t="s">
+        <v>241</v>
+      </c>
+      <c r="F103" t="s">
+        <v>452</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>718</v>
+      </c>
+      <c r="B104" t="s">
+        <v>719</v>
+      </c>
+      <c r="C104" t="s">
+        <v>238</v>
+      </c>
+      <c r="D104" t="s">
+        <v>239</v>
+      </c>
+      <c r="E104" t="s">
+        <v>241</v>
+      </c>
+      <c r="F104" t="s">
+        <v>241</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>721</v>
+      </c>
+      <c r="B105" t="s">
+        <v>722</v>
+      </c>
+      <c r="C105" t="s">
+        <v>723</v>
+      </c>
+      <c r="D105" t="s">
+        <v>239</v>
+      </c>
+      <c r="E105" t="s">
+        <v>440</v>
+      </c>
+      <c r="F105" t="s">
+        <v>241</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>725</v>
+      </c>
+      <c r="B106" t="s">
+        <v>726</v>
+      </c>
+      <c r="C106" t="s">
+        <v>727</v>
+      </c>
+      <c r="D106" t="s">
+        <v>239</v>
+      </c>
+      <c r="E106" t="s">
+        <v>728</v>
+      </c>
+      <c r="F106" t="s">
+        <v>729</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>731</v>
+      </c>
+      <c r="B107" t="s">
+        <v>732</v>
+      </c>
+      <c r="C107" t="s">
+        <v>40</v>
+      </c>
+      <c r="D107" t="s">
+        <v>239</v>
+      </c>
+      <c r="E107" t="s">
+        <v>321</v>
+      </c>
+      <c r="F107" t="s">
+        <v>733</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>735</v>
+      </c>
+      <c r="B108" t="s">
+        <v>580</v>
+      </c>
+      <c r="C108" t="s">
+        <v>493</v>
+      </c>
+      <c r="D108" t="s">
+        <v>239</v>
+      </c>
+      <c r="E108" t="s">
+        <v>736</v>
+      </c>
+      <c r="F108" t="s">
+        <v>737</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>739</v>
+      </c>
+      <c r="B109" t="s">
+        <v>740</v>
+      </c>
+      <c r="C109" t="s">
+        <v>309</v>
+      </c>
+      <c r="D109" t="s">
+        <v>239</v>
+      </c>
+      <c r="E109" t="s">
+        <v>741</v>
+      </c>
+      <c r="F109" t="s">
+        <v>742</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>744</v>
+      </c>
+      <c r="B110" t="s">
+        <v>745</v>
+      </c>
+      <c r="C110" t="s">
+        <v>493</v>
+      </c>
+      <c r="D110" t="s">
+        <v>239</v>
+      </c>
+      <c r="E110" t="s">
+        <v>241</v>
+      </c>
+      <c r="F110" t="s">
+        <v>729</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>747</v>
+      </c>
+      <c r="B111" t="s">
+        <v>748</v>
+      </c>
+      <c r="C111" t="s">
+        <v>493</v>
+      </c>
+      <c r="D111" t="s">
+        <v>239</v>
+      </c>
+      <c r="E111" t="s">
+        <v>749</v>
+      </c>
+      <c r="F111" t="s">
+        <v>750</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>752</v>
+      </c>
+      <c r="B112" t="s">
+        <v>753</v>
+      </c>
+      <c r="C112" t="s">
+        <v>238</v>
+      </c>
+      <c r="D112" t="s">
+        <v>258</v>
+      </c>
+      <c r="E112" t="s">
+        <v>754</v>
+      </c>
+      <c r="F112" t="s">
+        <v>755</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>757</v>
+      </c>
+      <c r="B113" t="s">
+        <v>758</v>
+      </c>
+      <c r="C113" t="s">
+        <v>759</v>
+      </c>
+      <c r="D113" t="s">
+        <v>239</v>
+      </c>
+      <c r="E113" t="s">
+        <v>760</v>
+      </c>
+      <c r="F113" t="s">
+        <v>761</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>763</v>
+      </c>
+      <c r="B114" t="s">
+        <v>764</v>
+      </c>
+      <c r="C114" t="s">
+        <v>238</v>
+      </c>
+      <c r="D114" t="s">
+        <v>239</v>
+      </c>
+      <c r="E114" t="s">
+        <v>241</v>
+      </c>
+      <c r="F114" t="s">
+        <v>765</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>767</v>
+      </c>
+      <c r="B115" t="s">
+        <v>411</v>
+      </c>
+      <c r="C115" t="s">
+        <v>412</v>
+      </c>
+      <c r="D115" t="s">
+        <v>239</v>
+      </c>
+      <c r="E115" t="s">
+        <v>768</v>
+      </c>
+      <c r="F115" t="s">
+        <v>414</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>770</v>
+      </c>
+      <c r="B116" t="s">
+        <v>771</v>
+      </c>
+      <c r="C116" t="s">
+        <v>772</v>
+      </c>
+      <c r="D116" t="s">
+        <v>239</v>
+      </c>
+      <c r="E116" t="s">
+        <v>773</v>
+      </c>
+      <c r="F116" t="s">
+        <v>774</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>775</v>
       </c>
     </row>
   </sheetData>
@@ -5048,6 +7202,50 @@
     <hyperlink ref="H70" r:id="rId69"/>
     <hyperlink ref="H71" r:id="rId70"/>
     <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5056,7 +7254,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5095,8 +7293,1066 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C2" t="s">
+        <v>778</v>
+      </c>
+      <c r="D2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" t="s">
+        <v>779</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>781</v>
+      </c>
+      <c r="B3" t="s">
+        <v>782</v>
+      </c>
+      <c r="C3" t="s">
+        <v>783</v>
+      </c>
+      <c r="D3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" t="s">
+        <v>784</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>786</v>
+      </c>
+      <c r="B4" t="s">
+        <v>787</v>
+      </c>
+      <c r="C4" t="s">
+        <v>783</v>
+      </c>
+      <c r="D4" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" t="s">
+        <v>784</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B5" t="s">
+        <v>789</v>
+      </c>
+      <c r="C5" t="s">
+        <v>783</v>
+      </c>
+      <c r="D5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" t="s">
+        <v>784</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>791</v>
+      </c>
+      <c r="B6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C6" t="s">
+        <v>793</v>
+      </c>
+      <c r="D6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" t="s">
+        <v>784</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>795</v>
+      </c>
+      <c r="B7" t="s">
+        <v>796</v>
+      </c>
+      <c r="C7" t="s">
+        <v>797</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" t="s">
+        <v>779</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>799</v>
+      </c>
+      <c r="B8" t="s">
+        <v>800</v>
+      </c>
+      <c r="C8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>803</v>
+      </c>
+      <c r="B9" t="s">
+        <v>804</v>
+      </c>
+      <c r="C9" t="s">
+        <v>805</v>
+      </c>
+      <c r="D9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F9" t="s">
+        <v>806</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B10" t="s">
+        <v>809</v>
+      </c>
+      <c r="C10" t="s">
+        <v>810</v>
+      </c>
+      <c r="D10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" t="s">
+        <v>811</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>813</v>
+      </c>
+      <c r="B11" t="s">
+        <v>814</v>
+      </c>
+      <c r="C11" t="s">
+        <v>815</v>
+      </c>
+      <c r="D11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F11" t="s">
+        <v>779</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>817</v>
+      </c>
+      <c r="B12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C12" t="s">
+        <v>819</v>
+      </c>
+      <c r="D12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" t="s">
+        <v>241</v>
+      </c>
+      <c r="F12" t="s">
+        <v>779</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>821</v>
+      </c>
+      <c r="B13" t="s">
+        <v>822</v>
+      </c>
+      <c r="C13" t="s">
+        <v>823</v>
+      </c>
+      <c r="D13" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" t="s">
+        <v>779</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>825</v>
+      </c>
+      <c r="B14" t="s">
+        <v>826</v>
+      </c>
+      <c r="C14" t="s">
+        <v>827</v>
+      </c>
+      <c r="D14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" t="s">
+        <v>806</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>829</v>
+      </c>
+      <c r="B15" t="s">
+        <v>830</v>
+      </c>
+      <c r="C15" t="s">
+        <v>783</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" t="s">
+        <v>831</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>833</v>
+      </c>
+      <c r="B16" t="s">
+        <v>834</v>
+      </c>
+      <c r="C16" t="s">
+        <v>835</v>
+      </c>
+      <c r="D16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" t="s">
+        <v>294</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>837</v>
+      </c>
+      <c r="B17" t="s">
+        <v>838</v>
+      </c>
+      <c r="C17" t="s">
+        <v>839</v>
+      </c>
+      <c r="D17" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" t="s">
+        <v>779</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>841</v>
+      </c>
+      <c r="B18" t="s">
+        <v>842</v>
+      </c>
+      <c r="C18" t="s">
+        <v>843</v>
+      </c>
+      <c r="D18" t="s">
+        <v>241</v>
+      </c>
+      <c r="E18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" t="s">
+        <v>779</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>845</v>
+      </c>
+      <c r="B19" t="s">
+        <v>846</v>
+      </c>
+      <c r="C19" t="s">
+        <v>847</v>
+      </c>
+      <c r="D19" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" t="s">
+        <v>241</v>
+      </c>
+      <c r="F19" t="s">
+        <v>779</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>849</v>
+      </c>
+      <c r="B20" t="s">
+        <v>850</v>
+      </c>
+      <c r="C20" t="s">
+        <v>851</v>
+      </c>
+      <c r="D20" t="s">
+        <v>241</v>
+      </c>
+      <c r="E20" t="s">
+        <v>241</v>
+      </c>
+      <c r="F20" t="s">
+        <v>852</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>854</v>
+      </c>
+      <c r="B21" t="s">
+        <v>855</v>
+      </c>
+      <c r="C21" t="s">
+        <v>856</v>
+      </c>
+      <c r="D21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" t="s">
+        <v>241</v>
+      </c>
+      <c r="F21" t="s">
+        <v>779</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>858</v>
+      </c>
+      <c r="B22" t="s">
+        <v>859</v>
+      </c>
+      <c r="C22" t="s">
+        <v>860</v>
+      </c>
+      <c r="D22" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" t="s">
+        <v>241</v>
+      </c>
+      <c r="F22" t="s">
+        <v>779</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>862</v>
+      </c>
+      <c r="B23" t="s">
+        <v>863</v>
+      </c>
+      <c r="C23" t="s">
+        <v>462</v>
+      </c>
+      <c r="D23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" t="s">
+        <v>784</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>865</v>
+      </c>
+      <c r="B24" t="s">
+        <v>866</v>
+      </c>
+      <c r="C24" t="s">
+        <v>783</v>
+      </c>
+      <c r="D24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" t="s">
+        <v>241</v>
+      </c>
+      <c r="F24" t="s">
+        <v>784</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>868</v>
+      </c>
+      <c r="B25" t="s">
+        <v>869</v>
+      </c>
+      <c r="C25" t="s">
+        <v>665</v>
+      </c>
+      <c r="D25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F25" t="s">
+        <v>784</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>871</v>
+      </c>
+      <c r="B26" t="s">
+        <v>872</v>
+      </c>
+      <c r="C26" t="s">
+        <v>873</v>
+      </c>
+      <c r="D26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" t="s">
+        <v>241</v>
+      </c>
+      <c r="F26" t="s">
+        <v>874</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>876</v>
+      </c>
+      <c r="B27" t="s">
+        <v>877</v>
+      </c>
+      <c r="C27" t="s">
+        <v>793</v>
+      </c>
+      <c r="D27" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" t="s">
+        <v>241</v>
+      </c>
+      <c r="F27" t="s">
+        <v>878</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>880</v>
+      </c>
+      <c r="B28" t="s">
+        <v>881</v>
+      </c>
+      <c r="C28" t="s">
+        <v>793</v>
+      </c>
+      <c r="D28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E28" t="s">
+        <v>241</v>
+      </c>
+      <c r="F28" t="s">
+        <v>852</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>883</v>
+      </c>
+      <c r="B29" t="s">
+        <v>877</v>
+      </c>
+      <c r="C29" t="s">
+        <v>793</v>
+      </c>
+      <c r="D29" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" t="s">
+        <v>241</v>
+      </c>
+      <c r="F29" t="s">
+        <v>878</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>885</v>
+      </c>
+      <c r="B30" t="s">
+        <v>800</v>
+      </c>
+      <c r="C30" t="s">
+        <v>801</v>
+      </c>
+      <c r="D30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" t="s">
+        <v>241</v>
+      </c>
+      <c r="F30" t="s">
+        <v>779</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>887</v>
+      </c>
+      <c r="B31" t="s">
+        <v>888</v>
+      </c>
+      <c r="C31" t="s">
+        <v>889</v>
+      </c>
+      <c r="D31" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" t="s">
+        <v>241</v>
+      </c>
+      <c r="F31" t="s">
+        <v>806</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>891</v>
+      </c>
+      <c r="B32" t="s">
+        <v>859</v>
+      </c>
+      <c r="C32" t="s">
+        <v>860</v>
+      </c>
+      <c r="D32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" t="s">
+        <v>241</v>
+      </c>
+      <c r="F32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>893</v>
+      </c>
+      <c r="B33" t="s">
+        <v>894</v>
+      </c>
+      <c r="C33" t="s">
+        <v>895</v>
+      </c>
+      <c r="D33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" t="s">
+        <v>241</v>
+      </c>
+      <c r="F33" t="s">
+        <v>294</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>897</v>
+      </c>
+      <c r="B34" t="s">
+        <v>898</v>
+      </c>
+      <c r="C34" t="s">
+        <v>899</v>
+      </c>
+      <c r="D34" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" t="s">
+        <v>779</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>897</v>
+      </c>
+      <c r="B35" t="s">
+        <v>901</v>
+      </c>
+      <c r="C35" t="s">
+        <v>902</v>
+      </c>
+      <c r="D35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" t="s">
+        <v>241</v>
+      </c>
+      <c r="F35" t="s">
+        <v>779</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>904</v>
+      </c>
+      <c r="B36" t="s">
+        <v>905</v>
+      </c>
+      <c r="C36" t="s">
+        <v>906</v>
+      </c>
+      <c r="D36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" t="s">
+        <v>241</v>
+      </c>
+      <c r="F36" t="s">
+        <v>852</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>908</v>
+      </c>
+      <c r="B37" t="s">
+        <v>909</v>
+      </c>
+      <c r="C37" t="s">
+        <v>910</v>
+      </c>
+      <c r="D37" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37" t="s">
+        <v>241</v>
+      </c>
+      <c r="F37" t="s">
+        <v>294</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>912</v>
+      </c>
+      <c r="B38" t="s">
+        <v>913</v>
+      </c>
+      <c r="C38" t="s">
+        <v>914</v>
+      </c>
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" t="s">
+        <v>779</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>916</v>
+      </c>
+      <c r="B39" t="s">
+        <v>917</v>
+      </c>
+      <c r="C39" t="s">
+        <v>918</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
+        <v>241</v>
+      </c>
+      <c r="F39" t="s">
+        <v>779</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>920</v>
+      </c>
+      <c r="B40" t="s">
+        <v>921</v>
+      </c>
+      <c r="C40" t="s">
+        <v>793</v>
+      </c>
+      <c r="D40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" t="s">
+        <v>241</v>
+      </c>
+      <c r="F40" t="s">
+        <v>779</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>923</v>
+      </c>
+      <c r="B41" t="s">
+        <v>924</v>
+      </c>
+      <c r="C41" t="s">
+        <v>925</v>
+      </c>
+      <c r="D41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" t="s">
+        <v>241</v>
+      </c>
+      <c r="F41" t="s">
+        <v>852</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>927</v>
+      </c>
+      <c r="B42" t="s">
+        <v>800</v>
+      </c>
+      <c r="C42" t="s">
+        <v>801</v>
+      </c>
+      <c r="D42" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" t="s">
+        <v>241</v>
+      </c>
+      <c r="F42" t="s">
+        <v>779</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>929</v>
+      </c>
+      <c r="B43" t="s">
+        <v>930</v>
+      </c>
+      <c r="C43" t="s">
+        <v>931</v>
+      </c>
+      <c r="D43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43" t="s">
+        <v>241</v>
+      </c>
+      <c r="F43" t="s">
+        <v>779</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>933</v>
+      </c>
+      <c r="B44" t="s">
+        <v>800</v>
+      </c>
+      <c r="C44" t="s">
+        <v>801</v>
+      </c>
+      <c r="D44" t="s">
+        <v>241</v>
+      </c>
+      <c r="E44" t="s">
+        <v>241</v>
+      </c>
+      <c r="F44" t="s">
+        <v>779</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>935</v>
+      </c>
+      <c r="B45" t="s">
+        <v>859</v>
+      </c>
+      <c r="C45" t="s">
+        <v>860</v>
+      </c>
+      <c r="D45" t="s">
+        <v>241</v>
+      </c>
+      <c r="E45" t="s">
+        <v>241</v>
+      </c>
+      <c r="F45" t="s">
+        <v>779</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>936</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
